--- a/files/excel-mastery-full.xlsx
+++ b/files/excel-mastery-full.xlsx
@@ -8,30 +8,30 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Mac\Home\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C7B57231-D6BA-42E1-A093-F1FFB517F084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D75F65E6-DCB5-4F65-A249-F4C3B5449CC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1605" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1605" yWindow="-16320" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-1_体裁の対比" sheetId="1" r:id="rId1"/>
     <sheet name="1-2_操作イメージ" sheetId="2" r:id="rId2"/>
-    <sheet name="2-1_実績集計" sheetId="3" r:id="rId3"/>
-    <sheet name="2-2_クリーニング" sheetId="4" r:id="rId4"/>
-    <sheet name="2-4_PL①Input" sheetId="5" r:id="rId5"/>
-    <sheet name="2-4_PL②計算" sheetId="6" r:id="rId6"/>
-    <sheet name="2-4_PL③Output" sheetId="7" r:id="rId7"/>
-    <sheet name="00_Index" sheetId="8" r:id="rId8"/>
-    <sheet name="01_Assumption" sheetId="9" r:id="rId9"/>
-    <sheet name="02_RawData" sheetId="10" r:id="rId10"/>
-    <sheet name="03_Master" sheetId="11" r:id="rId11"/>
-    <sheet name="04_Calculation" sheetId="12" r:id="rId12"/>
-    <sheet name="05_Output" sheetId="13" r:id="rId13"/>
-    <sheet name="06_Check" sheetId="14" r:id="rId14"/>
-    <sheet name="4-1_チェックセル" sheetId="15" r:id="rId15"/>
-    <sheet name="4-3_常識チェック" sheetId="16" r:id="rId16"/>
+    <sheet name="2-1_実績集計_SUMIFS" sheetId="3" r:id="rId3"/>
+    <sheet name="2-1_実績集計_XLOOKUP" sheetId="17" r:id="rId4"/>
+    <sheet name="2-2_クリーニング" sheetId="4" r:id="rId5"/>
+    <sheet name="2-4_PL①Input" sheetId="5" r:id="rId6"/>
+    <sheet name="2-4_PL②計算" sheetId="6" r:id="rId7"/>
+    <sheet name="2-4_PL③Output" sheetId="7" r:id="rId8"/>
+    <sheet name="00_Index" sheetId="8" r:id="rId9"/>
+    <sheet name="01_Assumption" sheetId="9" r:id="rId10"/>
+    <sheet name="02_RawData" sheetId="10" r:id="rId11"/>
+    <sheet name="03_Master" sheetId="11" r:id="rId12"/>
+    <sheet name="04_Calculation" sheetId="12" r:id="rId13"/>
+    <sheet name="05_Output" sheetId="13" r:id="rId14"/>
+    <sheet name="06_Check" sheetId="14" r:id="rId15"/>
+    <sheet name="4-1_チェックセル" sheetId="15" r:id="rId16"/>
+    <sheet name="4-3_常識チェック" sheetId="16" r:id="rId17"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="283">
   <si>
     <t>1-1. 体裁を統一できる ― 良い例と悪い例の対比</t>
   </si>
@@ -949,6 +949,95 @@
     </rPh>
     <phoneticPr fontId="11"/>
   </si>
+  <si>
+    <t>2-1. 実績集計 ― 元データと集計結果（XLOOKUP）</t>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>行</t>
+  </si>
+  <si>
+    <t>B 商品コード</t>
+  </si>
+  <si>
+    <t>C 商品名</t>
+  </si>
+  <si>
+    <t>D 数量</t>
+  </si>
+  <si>
+    <t>F 売上(円)</t>
+  </si>
+  <si>
+    <t>F-102</t>
+  </si>
+  <si>
+    <t>F-101</t>
+  </si>
+  <si>
+    <t>F-103</t>
+  </si>
+  <si>
+    <t>F-999</t>
+  </si>
+  <si>
+    <t>② 元データ：マスター</t>
+    <rPh sb="2" eb="3">
+      <t>モト</t>
+    </rPh>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>A 商品コード</t>
+  </si>
+  <si>
+    <t>B 商品名</t>
+  </si>
+  <si>
+    <t>C 原価(円)</t>
+  </si>
+  <si>
+    <t>金目鯛煮付</t>
+  </si>
+  <si>
+    <t>鮑ステーキ</t>
+  </si>
+  <si>
+    <t>地魚刺身盛</t>
+  </si>
+  <si>
+    <t>E 原価単価(円)</t>
+  </si>
+  <si>
+    <t>F 原価計(円)</t>
+  </si>
+  <si>
+    <t>売上</t>
+    <rPh sb="0" eb="2">
+      <t>ウリアゲ</t>
+    </rPh>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>原価率</t>
+    <rPh sb="0" eb="3">
+      <t>ゲンカリツ</t>
+    </rPh>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>③ 集計：商品別売上と原価率</t>
+    <rPh sb="5" eb="8">
+      <t>ショウヒンベツ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ウリアゲ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>ゲンカリツ</t>
+    </rPh>
+    <phoneticPr fontId="11"/>
+  </si>
 </sst>
 </file>
 
@@ -958,10 +1047,10 @@
     <numFmt numFmtId="176" formatCode="#,##0.0"/>
     <numFmt numFmtId="177" formatCode="0.0%"/>
     <numFmt numFmtId="178" formatCode="0.0"/>
-    <numFmt numFmtId="182" formatCode="#,##0%;[Red]\-#,##0%"/>
-    <numFmt numFmtId="186" formatCode="#,##0.00000"/>
-    <numFmt numFmtId="187" formatCode="#,##0.0%;[Red]\-#,##0.0%"/>
-    <numFmt numFmtId="188" formatCode="0.000"/>
+    <numFmt numFmtId="179" formatCode="#,##0%;[Red]\-#,##0%"/>
+    <numFmt numFmtId="180" formatCode="#,##0.00000"/>
+    <numFmt numFmtId="181" formatCode="#,##0.0%;[Red]\-#,##0.0%"/>
+    <numFmt numFmtId="182" formatCode="0.000"/>
   </numFmts>
   <fonts count="29" x14ac:knownFonts="1">
     <font>
@@ -1469,7 +1558,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="38" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
@@ -1477,8 +1566,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="189">
+  <cellXfs count="191">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1575,9 +1667,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1632,19 +1721,10 @@
     <xf numFmtId="177" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="6" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="6" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1659,30 +1739,9 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="38" fontId="13" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1797,243 +1856,287 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="16" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="24" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="24" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="24" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="13" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="24" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="25" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="22" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="22" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="17" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="28" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="28" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="13" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="13" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="16" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="16" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="28" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="28" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="28" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="23" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="23" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="16" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="24" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="24" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="24" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="13" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="24" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="25" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="17" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="17" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="22" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="22" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="13" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="22" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="17" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="38" fontId="9" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="186" fontId="28" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="186" fontId="28" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="22" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="13" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="13" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="13" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="13" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="16" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="16" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="188" fontId="28" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="188" fontId="28" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="188" fontId="28" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="23" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="23" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
+    <cellStyle name="パーセント" xfId="3" builtinId="5"/>
     <cellStyle name="桁区切り" xfId="1" builtinId="6"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
@@ -2467,16 +2570,16 @@
       <c r="D8" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="44">
+      <c r="E8" s="43">
         <v>30</v>
       </c>
-      <c r="F8" s="45">
+      <c r="F8" s="44">
         <v>30</v>
       </c>
-      <c r="G8" s="50">
+      <c r="G8" s="49">
         <v>0.68</v>
       </c>
-      <c r="H8" s="45">
+      <c r="H8" s="44">
         <v>52000</v>
       </c>
       <c r="I8" s="13">
@@ -2488,16 +2591,16 @@
       <c r="D9" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="46">
+      <c r="E9" s="45">
         <v>30</v>
       </c>
-      <c r="F9" s="47">
+      <c r="F9" s="46">
         <v>30</v>
       </c>
-      <c r="G9" s="51">
+      <c r="G9" s="50">
         <v>0.72</v>
       </c>
-      <c r="H9" s="47">
+      <c r="H9" s="46">
         <v>61000</v>
       </c>
       <c r="I9" s="14">
@@ -2509,16 +2612,16 @@
       <c r="D10" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="48">
+      <c r="E10" s="47">
         <v>3</v>
       </c>
-      <c r="F10" s="49">
+      <c r="F10" s="48">
         <v>30</v>
       </c>
-      <c r="G10" s="52">
+      <c r="G10" s="51">
         <v>0.65</v>
       </c>
-      <c r="H10" s="49">
+      <c r="H10" s="48">
         <v>150000</v>
       </c>
       <c r="I10" s="15">
@@ -2665,14 +2768,14 @@
       </c>
     </row>
     <row r="25" spans="3:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D25" s="108" t="s">
+      <c r="D25" s="167" t="s">
         <v>11</v>
       </c>
-      <c r="E25" s="109"/>
-      <c r="F25" s="109"/>
-      <c r="G25" s="109"/>
-      <c r="H25" s="110"/>
-      <c r="I25" s="43" t="e">
+      <c r="E25" s="168"/>
+      <c r="F25" s="168"/>
+      <c r="G25" s="168"/>
+      <c r="H25" s="169"/>
+      <c r="I25" s="42" t="e">
         <f>SUM(I22:I24)</f>
         <v>#VALUE!</v>
       </c>
@@ -2717,6 +2820,91 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="B2:F13"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="3" width="2.36328125" customWidth="1"/>
+    <col min="4" max="4" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="64" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D5" s="66" t="s">
+        <v>180</v>
+      </c>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+    </row>
+    <row r="6" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D7" s="68" t="s">
+        <v>105</v>
+      </c>
+      <c r="E7" s="68" t="s">
+        <v>106</v>
+      </c>
+      <c r="F7" s="68" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D8" s="109" t="s">
+        <v>150</v>
+      </c>
+      <c r="E8" s="165">
+        <v>0.1</v>
+      </c>
+      <c r="F8" s="68"/>
+    </row>
+    <row r="9" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D9" s="109" t="s">
+        <v>181</v>
+      </c>
+      <c r="E9" s="166">
+        <v>7</v>
+      </c>
+      <c r="F9" s="68" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D10" s="109" t="s">
+        <v>182</v>
+      </c>
+      <c r="E10" s="166">
+        <v>8</v>
+      </c>
+      <c r="F10" s="68" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D11" s="109" t="s">
+        <v>183</v>
+      </c>
+      <c r="E11" s="165">
+        <v>0.7</v>
+      </c>
+      <c r="F11" s="68"/>
+    </row>
+    <row r="12" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="13" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+  </sheetData>
+  <phoneticPr fontId="11"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="B2:I21"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
@@ -2730,7 +2918,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="75" t="s">
+      <c r="B2" s="64" t="s">
         <v>184</v>
       </c>
     </row>
@@ -2741,233 +2929,233 @@
       </c>
     </row>
     <row r="5" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D5" s="77" t="s">
+      <c r="D5" s="66" t="s">
         <v>185</v>
       </c>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
     </row>
     <row r="6" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="7" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D7" s="169" t="s">
+      <c r="D7" s="148" t="s">
         <v>66</v>
       </c>
-      <c r="E7" s="169" t="s">
+      <c r="E7" s="148" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="169" t="s">
+      <c r="F7" s="148" t="s">
         <v>47</v>
       </c>
-      <c r="G7" s="169" t="s">
+      <c r="G7" s="148" t="s">
         <v>67</v>
       </c>
-      <c r="H7" s="169" t="s">
+      <c r="H7" s="148" t="s">
         <v>68</v>
       </c>
-      <c r="I7" s="169" t="s">
+      <c r="I7" s="148" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="8" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D8" s="169" t="s">
+      <c r="D8" s="148" t="s">
         <v>70</v>
       </c>
-      <c r="E8" s="169" t="s">
+      <c r="E8" s="148" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="169">
+      <c r="F8" s="148">
         <v>7</v>
       </c>
-      <c r="G8" s="169" t="s">
+      <c r="G8" s="148" t="s">
         <v>61</v>
       </c>
-      <c r="H8" s="169">
+      <c r="H8" s="148">
         <v>2</v>
       </c>
-      <c r="I8" s="169">
+      <c r="I8" s="148">
         <v>160000</v>
       </c>
     </row>
     <row r="9" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D9" s="169" t="s">
+      <c r="D9" s="148" t="s">
         <v>71</v>
       </c>
-      <c r="E9" s="169" t="s">
+      <c r="E9" s="148" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="169">
+      <c r="F9" s="148">
         <v>7</v>
       </c>
-      <c r="G9" s="169" t="s">
+      <c r="G9" s="148" t="s">
         <v>72</v>
       </c>
-      <c r="H9" s="169">
+      <c r="H9" s="148">
         <v>3</v>
       </c>
-      <c r="I9" s="169">
+      <c r="I9" s="148">
         <v>108000</v>
       </c>
     </row>
     <row r="10" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D10" s="169" t="s">
+      <c r="D10" s="148" t="s">
         <v>73</v>
       </c>
-      <c r="E10" s="169" t="s">
+      <c r="E10" s="148" t="s">
         <v>9</v>
       </c>
-      <c r="F10" s="169">
+      <c r="F10" s="148">
         <v>7</v>
       </c>
-      <c r="G10" s="169" t="s">
+      <c r="G10" s="148" t="s">
         <v>72</v>
       </c>
-      <c r="H10" s="169">
+      <c r="H10" s="148">
         <v>2</v>
       </c>
-      <c r="I10" s="169">
+      <c r="I10" s="148">
         <v>72000</v>
       </c>
     </row>
     <row r="11" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D11" s="169" t="s">
+      <c r="D11" s="148" t="s">
         <v>74</v>
       </c>
-      <c r="E11" s="169" t="s">
+      <c r="E11" s="148" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="169">
+      <c r="F11" s="148">
         <v>8</v>
       </c>
-      <c r="G11" s="169" t="s">
+      <c r="G11" s="148" t="s">
         <v>61</v>
       </c>
-      <c r="H11" s="169">
+      <c r="H11" s="148">
         <v>2</v>
       </c>
-      <c r="I11" s="169">
+      <c r="I11" s="148">
         <v>180000</v>
       </c>
     </row>
     <row r="12" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D12" s="169" t="s">
+      <c r="D12" s="148" t="s">
         <v>75</v>
       </c>
-      <c r="E12" s="169" t="s">
+      <c r="E12" s="148" t="s">
         <v>9</v>
       </c>
-      <c r="F12" s="169">
+      <c r="F12" s="148">
         <v>8</v>
       </c>
-      <c r="G12" s="169" t="s">
+      <c r="G12" s="148" t="s">
         <v>61</v>
       </c>
-      <c r="H12" s="169">
+      <c r="H12" s="148">
         <v>1</v>
       </c>
-      <c r="I12" s="169">
+      <c r="I12" s="148">
         <v>95000</v>
       </c>
     </row>
     <row r="13" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D13" s="169" t="s">
+      <c r="D13" s="148" t="s">
         <v>76</v>
       </c>
-      <c r="E13" s="169" t="s">
+      <c r="E13" s="148" t="s">
         <v>8</v>
       </c>
-      <c r="F13" s="169">
+      <c r="F13" s="148">
         <v>7</v>
       </c>
-      <c r="G13" s="169" t="s">
+      <c r="G13" s="148" t="s">
         <v>72</v>
       </c>
-      <c r="H13" s="169">
+      <c r="H13" s="148">
         <v>1</v>
       </c>
-      <c r="I13" s="169">
+      <c r="I13" s="148">
         <v>36000</v>
       </c>
     </row>
     <row r="14" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D14" s="169" t="s">
+      <c r="D14" s="148" t="s">
         <v>77</v>
       </c>
-      <c r="E14" s="169" t="s">
+      <c r="E14" s="148" t="s">
         <v>9</v>
       </c>
-      <c r="F14" s="169">
+      <c r="F14" s="148">
         <v>8</v>
       </c>
-      <c r="G14" s="169" t="s">
+      <c r="G14" s="148" t="s">
         <v>72</v>
       </c>
-      <c r="H14" s="169">
+      <c r="H14" s="148">
         <v>4</v>
       </c>
-      <c r="I14" s="169">
+      <c r="I14" s="148">
         <v>152000</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D15" s="169" t="s">
+      <c r="D15" s="148" t="s">
         <v>78</v>
       </c>
-      <c r="E15" s="169" t="s">
+      <c r="E15" s="148" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="169">
+      <c r="F15" s="148">
         <v>8</v>
       </c>
-      <c r="G15" s="169" t="s">
+      <c r="G15" s="148" t="s">
         <v>72</v>
       </c>
-      <c r="H15" s="169">
+      <c r="H15" s="148">
         <v>2</v>
       </c>
-      <c r="I15" s="169">
+      <c r="I15" s="148">
         <v>74000</v>
       </c>
     </row>
     <row r="16" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D16" s="169" t="s">
+      <c r="D16" s="148" t="s">
         <v>79</v>
       </c>
-      <c r="E16" s="169" t="s">
+      <c r="E16" s="148" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="169">
+      <c r="F16" s="148">
         <v>7</v>
       </c>
-      <c r="G16" s="169" t="s">
+      <c r="G16" s="148" t="s">
         <v>61</v>
       </c>
-      <c r="H16" s="169">
+      <c r="H16" s="148">
         <v>1</v>
       </c>
-      <c r="I16" s="169">
+      <c r="I16" s="148">
         <v>92000</v>
       </c>
     </row>
     <row r="17" spans="4:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D17" s="169" t="s">
+      <c r="D17" s="148" t="s">
         <v>80</v>
       </c>
-      <c r="E17" s="169" t="s">
+      <c r="E17" s="148" t="s">
         <v>8</v>
       </c>
-      <c r="F17" s="169">
+      <c r="F17" s="148">
         <v>8</v>
       </c>
-      <c r="G17" s="169" t="s">
+      <c r="G17" s="148" t="s">
         <v>61</v>
       </c>
-      <c r="H17" s="169">
+      <c r="H17" s="148">
         <v>3</v>
       </c>
-      <c r="I17" s="169">
+      <c r="I17" s="148">
         <v>270000</v>
       </c>
     </row>
@@ -2981,7 +3169,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="B2:F13"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
@@ -2992,7 +3180,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="75" t="s">
+      <c r="B2" s="64" t="s">
         <v>188</v>
       </c>
     </row>
@@ -3001,65 +3189,65 @@
       <c r="D4" s="3"/>
     </row>
     <row r="5" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D5" s="77" t="s">
+      <c r="D5" s="66" t="s">
         <v>189</v>
       </c>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
     </row>
     <row r="6" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="7" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D7" s="79" t="s">
+      <c r="D7" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="79" t="s">
+      <c r="E7" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="F7" s="79" t="s">
+      <c r="F7" s="68" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="8" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D8" s="184" t="s">
+      <c r="D8" s="162" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="185">
+      <c r="E8" s="163">
         <v>20</v>
       </c>
-      <c r="F8" s="186" t="s">
+      <c r="F8" s="164" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="9" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D9" s="184" t="s">
+      <c r="D9" s="162" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="185">
+      <c r="E9" s="163">
         <v>15</v>
       </c>
-      <c r="F9" s="186" t="s">
+      <c r="F9" s="164" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="10" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D10" s="184"/>
-      <c r="E10" s="185"/>
-      <c r="F10" s="186"/>
+      <c r="D10" s="162"/>
+      <c r="E10" s="163"/>
+      <c r="F10" s="164"/>
     </row>
     <row r="11" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D11" s="184"/>
-      <c r="E11" s="185"/>
-      <c r="F11" s="186"/>
+      <c r="D11" s="162"/>
+      <c r="E11" s="163"/>
+      <c r="F11" s="164"/>
     </row>
     <row r="12" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D12" s="184"/>
-      <c r="E12" s="185"/>
-      <c r="F12" s="186"/>
+      <c r="D12" s="162"/>
+      <c r="E12" s="163"/>
+      <c r="F12" s="164"/>
     </row>
     <row r="13" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D13" s="184"/>
-      <c r="E13" s="185"/>
-      <c r="F13" s="186"/>
+      <c r="D13" s="162"/>
+      <c r="E13" s="163"/>
+      <c r="F13" s="164"/>
     </row>
   </sheetData>
   <phoneticPr fontId="11"/>
@@ -3067,7 +3255,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="B2:H13"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
@@ -3080,98 +3268,98 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="75" t="s">
+      <c r="B2" s="64" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D5" s="77" t="s">
+      <c r="D5" s="66" t="s">
         <v>193</v>
       </c>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
     </row>
     <row r="6" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="7" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D7" s="79" t="s">
+      <c r="D7" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="79" t="s">
+      <c r="E7" s="68" t="s">
         <v>85</v>
       </c>
-      <c r="F7" s="154" t="s">
+      <c r="F7" s="138" t="s">
         <v>260</v>
       </c>
-      <c r="G7" s="79" t="s">
+      <c r="G7" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="H7" s="79" t="s">
+      <c r="H7" s="68" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D8" s="80" t="s">
+      <c r="D8" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="96">
+      <c r="E8" s="85">
         <f>SUMIFS('02_RawData'!$I$8:$I$17,'02_RawData'!$E$8:$E$17,D8)</f>
         <v>828000</v>
       </c>
-      <c r="F8" s="174">
+      <c r="F8" s="152">
         <f>E8/$E$10</f>
         <v>0.66828087167070216</v>
       </c>
-      <c r="G8" s="96">
+      <c r="G8" s="85">
         <f>SUMIFS('03_Master'!$E$8:$E$9,'03_Master'!$D$8:$D$9,D8)</f>
         <v>20</v>
       </c>
-      <c r="H8" s="81">
+      <c r="H8" s="70">
         <f>E8/G8</f>
         <v>41400</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D9" s="139" t="s">
+      <c r="D9" s="123" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="123">
+      <c r="E9" s="108">
         <f>SUMIFS('02_RawData'!$I$8:$I$17,'02_RawData'!$E$8:$E$17,D9)</f>
         <v>411000</v>
       </c>
-      <c r="F9" s="175">
+      <c r="F9" s="153">
         <f t="shared" ref="F9:F10" si="0">E9/$E$10</f>
         <v>0.33171912832929784</v>
       </c>
-      <c r="G9" s="123">
+      <c r="G9" s="108">
         <f>SUMIFS('03_Master'!$E$8:$E$9,'03_Master'!$D$8:$D$9,D9)</f>
         <v>15</v>
       </c>
-      <c r="H9" s="170">
+      <c r="H9" s="149">
         <f>E9/G9</f>
         <v>27400</v>
       </c>
     </row>
     <row r="10" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D10" s="171" t="s">
+      <c r="D10" s="112" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="135">
+      <c r="E10" s="119">
         <f>SUM(E8:E9)</f>
         <v>1239000</v>
       </c>
-      <c r="F10" s="176">
+      <c r="F10" s="154">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G10" s="135">
+      <c r="G10" s="119">
         <f>SUM(G8:G9)</f>
         <v>35</v>
       </c>
-      <c r="H10" s="135"/>
+      <c r="H10" s="119"/>
     </row>
     <row r="11" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="12" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -3182,7 +3370,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="B2:E14"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
@@ -3192,54 +3380,54 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="75" t="s">
+      <c r="B2" s="64" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="3" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D5" s="77" t="s">
+      <c r="D5" s="66" t="s">
         <v>196</v>
       </c>
-      <c r="E5" s="78"/>
+      <c r="E5" s="67"/>
     </row>
     <row r="6" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="7" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D7" s="79" t="s">
+      <c r="D7" s="68" t="s">
         <v>197</v>
       </c>
-      <c r="E7" s="79" t="s">
+      <c r="E7" s="68" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="8" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D8" s="126" t="s">
+      <c r="D8" s="111" t="s">
         <v>198</v>
       </c>
-      <c r="E8" s="141">
+      <c r="E8" s="125">
         <f>'04_Calculation'!E10</f>
         <v>1239000</v>
       </c>
     </row>
     <row r="9" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D9" s="124"/>
-      <c r="E9" s="125"/>
+      <c r="D9" s="109"/>
+      <c r="E9" s="110"/>
     </row>
     <row r="10" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D10" s="80" t="s">
+      <c r="D10" s="69" t="s">
         <v>199</v>
       </c>
-      <c r="E10" s="172">
+      <c r="E10" s="150">
         <f>'04_Calculation'!F8</f>
         <v>0.66828087167070216</v>
       </c>
     </row>
     <row r="11" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D11" s="85" t="s">
+      <c r="D11" s="74" t="s">
         <v>200</v>
       </c>
-      <c r="E11" s="173">
+      <c r="E11" s="151">
         <f>'04_Calculation'!F9</f>
         <v>0.33171912832929784</v>
       </c>
@@ -3253,7 +3441,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="B2:H13"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
@@ -3265,7 +3453,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="75" t="s">
+      <c r="B2" s="64" t="s">
         <v>201</v>
       </c>
     </row>
@@ -3276,87 +3464,87 @@
       </c>
     </row>
     <row r="5" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D5" s="77" t="s">
+      <c r="D5" s="66" t="s">
         <v>202</v>
       </c>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
     </row>
     <row r="6" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="7" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D7" s="79" t="s">
+      <c r="D7" s="68" t="s">
         <v>202</v>
       </c>
-      <c r="E7" s="79" t="s">
+      <c r="E7" s="68" t="s">
         <v>203</v>
       </c>
-      <c r="F7" s="79" t="s">
+      <c r="F7" s="68" t="s">
         <v>204</v>
       </c>
-      <c r="G7" s="79"/>
-      <c r="H7" s="79" t="s">
+      <c r="G7" s="68"/>
+      <c r="H7" s="68" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D8" s="80" t="s">
+      <c r="D8" s="69" t="s">
         <v>206</v>
       </c>
-      <c r="E8" s="179">
+      <c r="E8" s="157">
         <f>COUNTA('02_RawData'!$D$8:$D$17)</f>
         <v>10</v>
       </c>
-      <c r="F8" s="177">
+      <c r="F8" s="155">
         <v>10</v>
       </c>
-      <c r="G8" s="181">
+      <c r="G8" s="159">
         <f>F8-E8</f>
         <v>0</v>
       </c>
-      <c r="H8" s="98" t="str">
+      <c r="H8" s="87" t="str">
         <f>IF(G8&lt;0.0001,"OK","要確認")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D9" s="83" t="s">
+      <c r="D9" s="72" t="s">
         <v>207</v>
       </c>
-      <c r="E9" s="119">
+      <c r="E9" s="105">
         <f>'04_Calculation'!E8+'04_Calculation'!E9</f>
         <v>1239000</v>
       </c>
-      <c r="F9" s="119">
+      <c r="F9" s="105">
         <f>'04_Calculation'!E10</f>
         <v>1239000</v>
       </c>
-      <c r="G9" s="182">
+      <c r="G9" s="160">
         <f t="shared" ref="G9:G10" si="0">F9-E9</f>
         <v>0</v>
       </c>
-      <c r="H9" s="99" t="str">
+      <c r="H9" s="88" t="str">
         <f t="shared" ref="H9:H10" si="1">IF(G9&lt;0.0001,"OK","要確認")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="10" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D10" s="85" t="s">
+      <c r="D10" s="74" t="s">
         <v>208</v>
       </c>
-      <c r="E10" s="180">
+      <c r="E10" s="158">
         <f>'05_Output'!E10+'05_Output'!E11</f>
         <v>1</v>
       </c>
-      <c r="F10" s="178">
+      <c r="F10" s="156">
         <v>1</v>
       </c>
-      <c r="G10" s="183">
+      <c r="G10" s="161">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H10" s="100" t="str">
+      <c r="H10" s="89" t="str">
         <f t="shared" si="1"/>
         <v>OK</v>
       </c>
@@ -3378,7 +3566,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="B2:H15"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
@@ -3391,7 +3579,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="75" t="s">
+      <c r="B2" s="64" t="s">
         <v>210</v>
       </c>
     </row>
@@ -3402,130 +3590,130 @@
       </c>
     </row>
     <row r="5" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D5" s="77" t="s">
+      <c r="D5" s="66" t="s">
         <v>212</v>
       </c>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
     </row>
     <row r="6" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="7" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D7" s="79" t="s">
+      <c r="D7" s="68" t="s">
         <v>202</v>
       </c>
-      <c r="E7" s="79" t="s">
+      <c r="E7" s="68" t="s">
         <v>203</v>
       </c>
-      <c r="F7" s="79" t="s">
+      <c r="F7" s="68" t="s">
         <v>204</v>
       </c>
-      <c r="G7" s="79" t="s">
+      <c r="G7" s="68" t="s">
         <v>213</v>
       </c>
-      <c r="H7" s="79" t="s">
+      <c r="H7" s="68" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D8" s="80" t="s">
+      <c r="D8" s="69" t="s">
         <v>214</v>
       </c>
-      <c r="E8" s="81">
+      <c r="E8" s="70">
         <v>84000000</v>
       </c>
-      <c r="F8" s="81">
+      <c r="F8" s="70">
         <v>84000000</v>
       </c>
-      <c r="G8" s="166">
+      <c r="G8" s="146">
         <f t="shared" ref="G8:G12" si="0">E8-F8</f>
         <v>0</v>
       </c>
-      <c r="H8" s="98" t="str">
+      <c r="H8" s="87" t="str">
         <f>IF(ABS(G8)&lt;1,"OK","要確認")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D9" s="83" t="s">
+      <c r="D9" s="72" t="s">
         <v>215</v>
       </c>
-      <c r="E9" s="84">
+      <c r="E9" s="73">
         <v>84000000</v>
       </c>
-      <c r="F9" s="84">
+      <c r="F9" s="73">
         <v>84000000</v>
       </c>
-      <c r="G9" s="167">
+      <c r="G9" s="147">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H9" s="99" t="str">
+      <c r="H9" s="88" t="str">
         <f>IF(ABS(G9)&lt;1,"OK","要確認")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="10" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D10" s="83" t="s">
+      <c r="D10" s="72" t="s">
         <v>216</v>
       </c>
-      <c r="E10" s="101">
+      <c r="E10" s="90">
         <v>1200</v>
       </c>
-      <c r="F10" s="101">
+      <c r="F10" s="90">
         <v>1200</v>
       </c>
-      <c r="G10" s="167">
+      <c r="G10" s="147">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H10" s="99" t="str">
+      <c r="H10" s="88" t="str">
         <f>IF(ABS(G10)&lt;1,"OK","要確認")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="11" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D11" s="83" t="s">
+      <c r="D11" s="72" t="s">
         <v>217</v>
       </c>
-      <c r="E11" s="84">
+      <c r="E11" s="73">
         <v>92400000</v>
       </c>
-      <c r="F11" s="84">
+      <c r="F11" s="73">
         <v>92400000</v>
       </c>
-      <c r="G11" s="167">
+      <c r="G11" s="147">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H11" s="99" t="str">
+      <c r="H11" s="88" t="str">
         <f>IF(ABS(G11)&lt;1,"OK","要確認")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="12" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D12" s="83" t="s">
+      <c r="D12" s="72" t="s">
         <v>218</v>
       </c>
-      <c r="E12" s="97">
+      <c r="E12" s="86">
         <v>1</v>
       </c>
-      <c r="F12" s="97">
+      <c r="F12" s="86">
         <v>0.99834336000000001</v>
       </c>
-      <c r="G12" s="167">
+      <c r="G12" s="147">
         <f t="shared" si="0"/>
         <v>1.656639999999987E-3</v>
       </c>
-      <c r="H12" s="99" t="str">
+      <c r="H12" s="88" t="str">
         <f>IF(ABS(G12)&lt;0.0001,"OK","要確認")</f>
         <v>要確認</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="14" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D14" s="76"/>
+      <c r="D14" s="65"/>
     </row>
     <row r="15" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
@@ -3542,7 +3730,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="B2:H13"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
@@ -3556,7 +3744,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="75" t="s">
+      <c r="B2" s="64" t="s">
         <v>219</v>
       </c>
     </row>
@@ -3567,89 +3755,89 @@
       </c>
     </row>
     <row r="5" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D5" s="77" t="s">
+      <c r="D5" s="66" t="s">
         <v>221</v>
       </c>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
     </row>
     <row r="6" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="7" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D7" s="79" t="s">
+      <c r="D7" s="68" t="s">
         <v>222</v>
       </c>
-      <c r="E7" s="79" t="s">
+      <c r="E7" s="68" t="s">
         <v>106</v>
       </c>
-      <c r="F7" s="79" t="s">
+      <c r="F7" s="68" t="s">
         <v>223</v>
       </c>
-      <c r="G7" s="79" t="s">
+      <c r="G7" s="68" t="s">
         <v>205</v>
       </c>
-      <c r="H7" s="79" t="s">
+      <c r="H7" s="68" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D8" s="80" t="s">
+      <c r="D8" s="69" t="s">
         <v>225</v>
       </c>
-      <c r="E8" s="81">
+      <c r="E8" s="70">
         <v>15</v>
       </c>
-      <c r="F8" s="88" t="s">
+      <c r="F8" s="77" t="s">
         <v>226</v>
       </c>
-      <c r="G8" s="102" t="str">
+      <c r="G8" s="91" t="str">
         <f>IF(E8&lt;=10,"OK","異常")</f>
         <v>異常</v>
       </c>
-      <c r="H8" s="103" t="s">
+      <c r="H8" s="92" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D9" s="83" t="s">
+      <c r="D9" s="72" t="s">
         <v>228</v>
       </c>
-      <c r="E9" s="97">
+      <c r="E9" s="86">
         <v>0.05</v>
       </c>
-      <c r="F9" s="90" t="s">
+      <c r="F9" s="79" t="s">
         <v>229</v>
       </c>
-      <c r="G9" s="104" t="str">
+      <c r="G9" s="93" t="str">
         <f>IF(AND(E9&gt;=0.2,E9&lt;=0.4),"OK","異常")</f>
         <v>異常</v>
       </c>
-      <c r="H9" s="105" t="s">
+      <c r="H9" s="94" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="10" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D10" s="85" t="s">
+      <c r="D10" s="74" t="s">
         <v>231</v>
       </c>
-      <c r="E10" s="86">
+      <c r="E10" s="75">
         <v>50000</v>
       </c>
-      <c r="F10" s="94" t="s">
+      <c r="F10" s="83" t="s">
         <v>232</v>
       </c>
-      <c r="G10" s="106" t="str">
+      <c r="G10" s="95" t="str">
         <f>IF(AND(E10&gt;=250000,E10&lt;=400000),"OK","異常")</f>
         <v>異常</v>
       </c>
-      <c r="H10" s="107" t="s">
+      <c r="H10" s="96" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="11" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="12" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D12" s="76" t="s">
+      <c r="D12" s="65" t="s">
         <v>234</v>
       </c>
     </row>
@@ -3700,15 +3888,15 @@
       <c r="D7" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="34" t="s">
+      <c r="E7" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="34"/>
-      <c r="G7" s="34" t="s">
+      <c r="F7" s="33"/>
+      <c r="G7" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="H7" s="34"/>
-      <c r="I7" s="34"/>
+      <c r="H7" s="33"/>
+      <c r="I7" s="33"/>
     </row>
     <row r="8" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D8" s="10" t="s">
@@ -3775,43 +3963,43 @@
       <c r="D14" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="E14" s="42" t="s">
+      <c r="E14" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="34"/>
+      <c r="H14" s="34"/>
+      <c r="I14" s="34"/>
     </row>
     <row r="15" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D15" s="36" t="s">
+      <c r="D15" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="E15" s="37">
+      <c r="E15" s="36">
         <v>7072000</v>
       </c>
     </row>
     <row r="16" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D16" s="38" t="s">
+      <c r="D16" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="E16" s="39">
+      <c r="E16" s="38">
         <v>8130000</v>
       </c>
     </row>
     <row r="17" spans="3:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D17" s="38" t="s">
+      <c r="D17" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="E17" s="39">
+      <c r="E17" s="38">
         <v>6540000</v>
       </c>
     </row>
     <row r="18" spans="3:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D18" s="40" t="s">
+      <c r="D18" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="E18" s="41">
+      <c r="E18" s="40">
         <v>5980000</v>
       </c>
     </row>
@@ -3858,10 +4046,10 @@
       <c r="D27" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="E27" s="44">
+      <c r="E27" s="43">
         <v>12000</v>
       </c>
-      <c r="F27" s="45">
+      <c r="F27" s="44">
         <v>30</v>
       </c>
       <c r="G27" s="13">
@@ -3873,13 +4061,13 @@
       <c r="D28" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="E28" s="46">
+      <c r="E28" s="45">
         <v>18000</v>
       </c>
-      <c r="F28" s="47">
+      <c r="F28" s="46">
         <v>22</v>
       </c>
-      <c r="G28" s="39">
+      <c r="G28" s="38">
         <f t="shared" ref="G28:G29" si="0">E28*F28</f>
         <v>396000</v>
       </c>
@@ -3888,13 +4076,13 @@
       <c r="D29" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="E29" s="48">
+      <c r="E29" s="47">
         <v>52000</v>
       </c>
-      <c r="F29" s="49">
+      <c r="F29" s="48">
         <v>8</v>
       </c>
-      <c r="G29" s="41">
+      <c r="G29" s="40">
         <f t="shared" si="0"/>
         <v>416000</v>
       </c>
@@ -3938,120 +4126,120 @@
       <c r="D38" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="E38" s="59">
+      <c r="E38" s="55">
         <v>10000</v>
       </c>
-      <c r="F38" s="59">
+      <c r="F38" s="55">
         <v>20000</v>
       </c>
-      <c r="G38" s="59">
+      <c r="G38" s="55">
         <v>30000</v>
       </c>
-      <c r="H38" s="59">
+      <c r="H38" s="55">
         <v>50000</v>
       </c>
     </row>
     <row r="39" spans="4:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D39" s="45">
+      <c r="D39" s="44">
         <v>1</v>
       </c>
       <c r="E39" s="13">
         <f t="shared" ref="E39:H43" si="1">$D39*E$38</f>
         <v>10000</v>
       </c>
-      <c r="F39" s="54">
+      <c r="F39" s="52">
         <f t="shared" si="1"/>
         <v>20000</v>
       </c>
-      <c r="G39" s="54">
+      <c r="G39" s="52">
         <f t="shared" si="1"/>
         <v>30000</v>
       </c>
-      <c r="H39" s="54">
+      <c r="H39" s="52">
         <f t="shared" si="1"/>
         <v>50000</v>
       </c>
     </row>
     <row r="40" spans="4:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D40" s="47">
+      <c r="D40" s="46">
         <v>2</v>
       </c>
-      <c r="E40" s="39">
+      <c r="E40" s="38">
         <f t="shared" si="1"/>
         <v>20000</v>
       </c>
-      <c r="F40" s="56">
+      <c r="F40" s="53">
         <f t="shared" si="1"/>
         <v>40000</v>
       </c>
-      <c r="G40" s="56">
+      <c r="G40" s="53">
         <f t="shared" si="1"/>
         <v>60000</v>
       </c>
-      <c r="H40" s="56">
+      <c r="H40" s="53">
         <f t="shared" si="1"/>
         <v>100000</v>
       </c>
     </row>
     <row r="41" spans="4:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D41" s="47">
+      <c r="D41" s="46">
         <v>3</v>
       </c>
-      <c r="E41" s="39">
+      <c r="E41" s="38">
         <f t="shared" si="1"/>
         <v>30000</v>
       </c>
-      <c r="F41" s="56">
+      <c r="F41" s="53">
         <f t="shared" si="1"/>
         <v>60000</v>
       </c>
-      <c r="G41" s="56">
+      <c r="G41" s="53">
         <f t="shared" si="1"/>
         <v>90000</v>
       </c>
-      <c r="H41" s="56">
+      <c r="H41" s="53">
         <f t="shared" si="1"/>
         <v>150000</v>
       </c>
     </row>
     <row r="42" spans="4:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D42" s="47">
+      <c r="D42" s="46">
         <v>5</v>
       </c>
-      <c r="E42" s="39">
+      <c r="E42" s="38">
         <f t="shared" si="1"/>
         <v>50000</v>
       </c>
-      <c r="F42" s="56">
+      <c r="F42" s="53">
         <f t="shared" si="1"/>
         <v>100000</v>
       </c>
-      <c r="G42" s="56">
+      <c r="G42" s="53">
         <f t="shared" si="1"/>
         <v>150000</v>
       </c>
-      <c r="H42" s="56">
+      <c r="H42" s="53">
         <f t="shared" si="1"/>
         <v>250000</v>
       </c>
     </row>
     <row r="43" spans="4:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D43" s="49">
+      <c r="D43" s="48">
         <v>10</v>
       </c>
-      <c r="E43" s="41">
+      <c r="E43" s="40">
         <f t="shared" si="1"/>
         <v>100000</v>
       </c>
-      <c r="F43" s="58">
+      <c r="F43" s="54">
         <f t="shared" si="1"/>
         <v>200000</v>
       </c>
-      <c r="G43" s="58">
+      <c r="G43" s="54">
         <f t="shared" si="1"/>
         <v>300000</v>
       </c>
-      <c r="H43" s="58">
+      <c r="H43" s="54">
         <f t="shared" si="1"/>
         <v>500000</v>
       </c>
@@ -4080,7 +4268,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B2:J38"/>
+  <dimension ref="B2:J47"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="2.36328125" customWidth="1"/>
@@ -4119,255 +4307,255 @@
       <c r="D6" s="2"/>
     </row>
     <row r="7" spans="2:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D7" s="33" t="s">
+      <c r="D7" s="171" t="s">
         <v>66</v>
       </c>
-      <c r="E7" s="33" t="s">
+      <c r="E7" s="171" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="33" t="s">
+      <c r="F7" s="171" t="s">
         <v>47</v>
       </c>
-      <c r="G7" s="33" t="s">
+      <c r="G7" s="171" t="s">
         <v>67</v>
       </c>
-      <c r="H7" s="33" t="s">
+      <c r="H7" s="171" t="s">
         <v>68</v>
       </c>
-      <c r="I7" s="33" t="s">
+      <c r="I7" s="171" t="s">
         <v>69</v>
       </c>
-      <c r="J7" s="33" t="s">
+      <c r="J7" s="171" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="8" spans="2:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D8" s="61" t="s">
+      <c r="D8" s="172" t="s">
         <v>70</v>
       </c>
-      <c r="E8" s="61" t="s">
+      <c r="E8" s="172" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="62">
+      <c r="F8" s="189">
         <v>7</v>
       </c>
-      <c r="G8" s="61" t="s">
+      <c r="G8" s="172" t="s">
         <v>61</v>
       </c>
-      <c r="H8" s="67">
+      <c r="H8" s="173">
         <v>2</v>
       </c>
-      <c r="I8" s="53">
+      <c r="I8" s="173">
         <v>4</v>
       </c>
-      <c r="J8" s="53">
+      <c r="J8" s="173">
         <v>160000</v>
       </c>
     </row>
     <row r="9" spans="2:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D9" s="63" t="s">
+      <c r="D9" s="172" t="s">
         <v>71</v>
       </c>
-      <c r="E9" s="63" t="s">
+      <c r="E9" s="172" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="64">
+      <c r="F9" s="189">
         <v>7</v>
       </c>
-      <c r="G9" s="63" t="s">
+      <c r="G9" s="172" t="s">
         <v>72</v>
       </c>
-      <c r="H9" s="68">
+      <c r="H9" s="173">
         <v>3</v>
       </c>
-      <c r="I9" s="55">
+      <c r="I9" s="173">
         <v>4</v>
       </c>
-      <c r="J9" s="55">
+      <c r="J9" s="173">
         <v>108000</v>
       </c>
     </row>
     <row r="10" spans="2:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D10" s="63" t="s">
+      <c r="D10" s="172" t="s">
         <v>73</v>
       </c>
-      <c r="E10" s="63" t="s">
+      <c r="E10" s="172" t="s">
         <v>9</v>
       </c>
-      <c r="F10" s="64">
+      <c r="F10" s="189">
         <v>7</v>
       </c>
-      <c r="G10" s="63" t="s">
+      <c r="G10" s="172" t="s">
         <v>72</v>
       </c>
-      <c r="H10" s="68">
+      <c r="H10" s="173">
         <v>2</v>
       </c>
-      <c r="I10" s="55">
+      <c r="I10" s="173">
         <v>3</v>
       </c>
-      <c r="J10" s="55">
+      <c r="J10" s="173">
         <v>72000</v>
       </c>
     </row>
     <row r="11" spans="2:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D11" s="63" t="s">
+      <c r="D11" s="172" t="s">
         <v>74</v>
       </c>
-      <c r="E11" s="63" t="s">
+      <c r="E11" s="172" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="64">
+      <c r="F11" s="189">
         <v>8</v>
       </c>
-      <c r="G11" s="63" t="s">
+      <c r="G11" s="172" t="s">
         <v>61</v>
       </c>
-      <c r="H11" s="68">
+      <c r="H11" s="173">
         <v>2</v>
       </c>
-      <c r="I11" s="55">
+      <c r="I11" s="173">
         <v>2</v>
       </c>
-      <c r="J11" s="55">
+      <c r="J11" s="173">
         <v>180000</v>
       </c>
     </row>
     <row r="12" spans="2:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D12" s="63" t="s">
+      <c r="D12" s="172" t="s">
         <v>75</v>
       </c>
-      <c r="E12" s="63" t="s">
+      <c r="E12" s="172" t="s">
         <v>9</v>
       </c>
-      <c r="F12" s="64">
+      <c r="F12" s="189">
         <v>8</v>
       </c>
-      <c r="G12" s="63" t="s">
+      <c r="G12" s="172" t="s">
         <v>61</v>
       </c>
-      <c r="H12" s="68">
+      <c r="H12" s="173">
         <v>1</v>
       </c>
-      <c r="I12" s="55">
+      <c r="I12" s="173">
         <v>2</v>
       </c>
-      <c r="J12" s="55">
+      <c r="J12" s="173">
         <v>95000</v>
       </c>
     </row>
     <row r="13" spans="2:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D13" s="63" t="s">
+      <c r="D13" s="172" t="s">
         <v>76</v>
       </c>
-      <c r="E13" s="63" t="s">
+      <c r="E13" s="172" t="s">
         <v>8</v>
       </c>
-      <c r="F13" s="64">
+      <c r="F13" s="189">
         <v>7</v>
       </c>
-      <c r="G13" s="63" t="s">
+      <c r="G13" s="172" t="s">
         <v>72</v>
       </c>
-      <c r="H13" s="68">
+      <c r="H13" s="173">
         <v>1</v>
       </c>
-      <c r="I13" s="55">
+      <c r="I13" s="173">
         <v>2</v>
       </c>
-      <c r="J13" s="55">
+      <c r="J13" s="173">
         <v>36000</v>
       </c>
     </row>
     <row r="14" spans="2:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D14" s="63" t="s">
+      <c r="D14" s="172" t="s">
         <v>77</v>
       </c>
-      <c r="E14" s="63" t="s">
+      <c r="E14" s="172" t="s">
         <v>9</v>
       </c>
-      <c r="F14" s="64">
+      <c r="F14" s="189">
         <v>8</v>
       </c>
-      <c r="G14" s="63" t="s">
+      <c r="G14" s="172" t="s">
         <v>72</v>
       </c>
-      <c r="H14" s="68">
+      <c r="H14" s="173">
         <v>4</v>
       </c>
-      <c r="I14" s="55">
+      <c r="I14" s="173">
         <v>6</v>
       </c>
-      <c r="J14" s="55">
+      <c r="J14" s="173">
         <v>152000</v>
       </c>
     </row>
     <row r="15" spans="2:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D15" s="63" t="s">
+      <c r="D15" s="172" t="s">
         <v>78</v>
       </c>
-      <c r="E15" s="63" t="s">
+      <c r="E15" s="172" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="64">
+      <c r="F15" s="189">
         <v>8</v>
       </c>
-      <c r="G15" s="63" t="s">
+      <c r="G15" s="172" t="s">
         <v>72</v>
       </c>
-      <c r="H15" s="68">
+      <c r="H15" s="173">
         <v>2</v>
       </c>
-      <c r="I15" s="55">
+      <c r="I15" s="173">
         <v>3</v>
       </c>
-      <c r="J15" s="55">
+      <c r="J15" s="173">
         <v>74000</v>
       </c>
     </row>
     <row r="16" spans="2:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D16" s="63" t="s">
+      <c r="D16" s="172" t="s">
         <v>79</v>
       </c>
-      <c r="E16" s="63" t="s">
+      <c r="E16" s="172" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="64">
+      <c r="F16" s="189">
         <v>7</v>
       </c>
-      <c r="G16" s="63" t="s">
+      <c r="G16" s="172" t="s">
         <v>61</v>
       </c>
-      <c r="H16" s="68">
+      <c r="H16" s="173">
         <v>1</v>
       </c>
-      <c r="I16" s="55">
+      <c r="I16" s="173">
         <v>2</v>
       </c>
-      <c r="J16" s="55">
+      <c r="J16" s="173">
         <v>92000</v>
       </c>
     </row>
     <row r="17" spans="3:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D17" s="65" t="s">
+      <c r="D17" s="172" t="s">
         <v>80</v>
       </c>
-      <c r="E17" s="65" t="s">
+      <c r="E17" s="172" t="s">
         <v>8</v>
       </c>
-      <c r="F17" s="66">
+      <c r="F17" s="189">
         <v>8</v>
       </c>
-      <c r="G17" s="65" t="s">
+      <c r="G17" s="172" t="s">
         <v>61</v>
       </c>
-      <c r="H17" s="69">
+      <c r="H17" s="173">
         <v>3</v>
       </c>
-      <c r="I17" s="57">
+      <c r="I17" s="173">
         <v>5</v>
       </c>
-      <c r="J17" s="57">
+      <c r="J17" s="173">
         <v>270000</v>
       </c>
     </row>
@@ -4402,52 +4590,52 @@
       </c>
     </row>
     <row r="24" spans="3:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D24" s="61" t="s">
+      <c r="D24" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="E24" s="72">
+      <c r="E24" s="61">
         <f>SUMIFS($J$8:$J$17,$E$8:$E$17,$D24,$F$8:$F$17,E$23)</f>
         <v>304000</v>
       </c>
-      <c r="F24" s="70">
+      <c r="F24" s="59">
         <f>SUMIFS($J$8:$J$17,$E$8:$E$17,$D24,$F$8:$F$17,F$23)</f>
         <v>524000</v>
       </c>
-      <c r="G24" s="72">
+      <c r="G24" s="61">
         <f>SUM(E24:F24)</f>
         <v>828000</v>
       </c>
     </row>
     <row r="25" spans="3:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D25" s="65" t="s">
+      <c r="D25" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="E25" s="73">
+      <c r="E25" s="62">
         <f>SUMIFS($J$8:$J$17,$E$8:$E$17,$D25,$F$8:$F$17,E$23)</f>
         <v>164000</v>
       </c>
-      <c r="F25" s="71">
+      <c r="F25" s="60">
         <f>SUMIFS($J$8:$J$17,$E$8:$E$17,$D25,$F$8:$F$17,F$23)</f>
         <v>247000</v>
       </c>
-      <c r="G25" s="73">
+      <c r="G25" s="62">
         <f>SUM(E25:F25)</f>
         <v>411000</v>
       </c>
     </row>
     <row r="26" spans="3:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D26" s="60" t="s">
+      <c r="D26" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="E26" s="74">
+      <c r="E26" s="63">
         <f>SUM(E24:E25)</f>
         <v>468000</v>
       </c>
-      <c r="F26" s="74">
+      <c r="F26" s="63">
         <f>SUM(F24:F25)</f>
         <v>771000</v>
       </c>
-      <c r="G26" s="74">
+      <c r="G26" s="63">
         <f>SUM(G24:G25)</f>
         <v>1239000</v>
       </c>
@@ -4486,49 +4674,55 @@
       </c>
     </row>
     <row r="35" spans="4:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D35" s="61" t="s">
+      <c r="D35" s="57" t="s">
         <v>61</v>
       </c>
-      <c r="E35" s="72">
+      <c r="E35" s="61">
         <f>SUMIFS($J$8:$J$17,$G$8:$G$17,D35)</f>
         <v>797000</v>
       </c>
-      <c r="F35" s="70">
+      <c r="F35" s="59">
         <f>SUMIFS($H$8:$H$17,$G$8:$G$17,D35)</f>
         <v>9</v>
       </c>
-      <c r="G35" s="72">
+      <c r="G35" s="61">
         <f>E35/F35</f>
         <v>88555.555555555562</v>
       </c>
     </row>
     <row r="36" spans="4:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D36" s="65" t="s">
+      <c r="D36" s="58" t="s">
         <v>72</v>
       </c>
-      <c r="E36" s="73">
+      <c r="E36" s="62">
         <f>SUMIFS($J$8:$J$17,$G$8:$G$17,D36)</f>
         <v>442000</v>
       </c>
-      <c r="F36" s="71">
+      <c r="F36" s="60">
         <f>SUMIFS($H$8:$H$17,$G$8:$G$17,D36)</f>
         <v>12</v>
       </c>
-      <c r="G36" s="73">
+      <c r="G36" s="62">
         <f>E36/F36</f>
         <v>36833.333333333336</v>
       </c>
     </row>
     <row r="37" spans="4:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D37" s="60"/>
-      <c r="E37" s="74"/>
-      <c r="F37" s="74"/>
-      <c r="G37" s="74"/>
+      <c r="D37" s="56"/>
+      <c r="E37" s="63"/>
+      <c r="F37" s="63"/>
+      <c r="G37" s="63"/>
     </row>
     <row r="38" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D38" s="3" t="s">
         <v>87</v>
       </c>
+    </row>
+    <row r="47" spans="4:7" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="D47" s="56"/>
+      <c r="E47" s="63"/>
+      <c r="F47" s="63"/>
+      <c r="G47" s="63"/>
     </row>
   </sheetData>
   <phoneticPr fontId="11"/>
@@ -4537,8 +4731,356 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DC6506F-00A7-41A7-9E89-2C33DCC4D02B}">
+  <dimension ref="B2:K31"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="3" width="2.36328125" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="10" width="12.26953125" customWidth="1"/>
+    <col min="11" max="11" width="9.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C2" s="1"/>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+    </row>
+    <row r="5" spans="2:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C5" s="2"/>
+      <c r="D5" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+    </row>
+    <row r="6" spans="2:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" spans="2:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D7" s="171" t="s">
+        <v>262</v>
+      </c>
+      <c r="E7" s="171" t="s">
+        <v>263</v>
+      </c>
+      <c r="F7" s="171" t="s">
+        <v>265</v>
+      </c>
+      <c r="G7" s="171" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D8" s="172">
+        <v>2</v>
+      </c>
+      <c r="E8" s="172" t="s">
+        <v>267</v>
+      </c>
+      <c r="F8" s="172">
+        <v>4</v>
+      </c>
+      <c r="G8" s="173">
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D9" s="172">
+        <v>3</v>
+      </c>
+      <c r="E9" s="172" t="s">
+        <v>268</v>
+      </c>
+      <c r="F9" s="172">
+        <v>6</v>
+      </c>
+      <c r="G9" s="173">
+        <v>27000</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D10" s="172">
+        <v>4</v>
+      </c>
+      <c r="E10" s="172" t="s">
+        <v>269</v>
+      </c>
+      <c r="F10" s="172">
+        <v>5</v>
+      </c>
+      <c r="G10" s="173">
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D11" s="172">
+        <v>5</v>
+      </c>
+      <c r="E11" s="172" t="s">
+        <v>270</v>
+      </c>
+      <c r="F11" s="172">
+        <v>2</v>
+      </c>
+      <c r="G11" s="173">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C15" s="2"/>
+      <c r="D15" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="17"/>
+    </row>
+    <row r="16" spans="2:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17" spans="4:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D17" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="18" spans="4:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D18" s="162" t="s">
+        <v>268</v>
+      </c>
+      <c r="E18" s="190" t="s">
+        <v>275</v>
+      </c>
+      <c r="F18" s="190">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="19" spans="4:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D19" s="162" t="s">
+        <v>267</v>
+      </c>
+      <c r="E19" s="190" t="s">
+        <v>276</v>
+      </c>
+      <c r="F19" s="190">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="20" spans="4:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D20" s="162" t="s">
+        <v>269</v>
+      </c>
+      <c r="E20" s="190" t="s">
+        <v>277</v>
+      </c>
+      <c r="F20" s="190">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="25" spans="4:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D25" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="17"/>
+    </row>
+    <row r="26" spans="4:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D26" s="2"/>
+    </row>
+    <row r="27" spans="4:11" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="D27" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="K27" s="6" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="28" spans="4:11" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="D28" s="101">
+        <v>2</v>
+      </c>
+      <c r="E28" s="175" t="s">
+        <v>267</v>
+      </c>
+      <c r="F28" s="175" t="str">
+        <f t="shared" ref="F28:F30" si="0">_xlfn.XLOOKUP($E28,$D$17:$D$20,E$17:E$20,"該当なし")</f>
+        <v>鮑ステーキ</v>
+      </c>
+      <c r="G28" s="174">
+        <f>SUMIFS($F$8:$F$11,$E$8:$E$11,E28)</f>
+        <v>4</v>
+      </c>
+      <c r="H28" s="183">
+        <f>_xlfn.XLOOKUP($E28,$D$17:$D$20,F$17:F$20,"該当なし")</f>
+        <v>3200</v>
+      </c>
+      <c r="I28" s="186">
+        <f t="shared" ref="I28:I30" si="1">IFERROR(G28*H28,"-")</f>
+        <v>12800</v>
+      </c>
+      <c r="J28" s="186">
+        <f>SUMIFS($G$8:$G$11,$E$8:$E$11,E28)</f>
+        <v>32000</v>
+      </c>
+      <c r="K28" s="176">
+        <f t="shared" ref="K28:K30" si="2">IFERROR(I28/J28,"-")</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="29" spans="4:11" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="D29" s="104">
+        <v>3</v>
+      </c>
+      <c r="E29" s="178" t="s">
+        <v>268</v>
+      </c>
+      <c r="F29" s="178" t="str">
+        <f t="shared" si="0"/>
+        <v>金目鯛煮付</v>
+      </c>
+      <c r="G29" s="177">
+        <f t="shared" ref="G29:G31" si="3">SUMIFS($F$8:$F$11,$E$8:$E$11,E29)</f>
+        <v>6</v>
+      </c>
+      <c r="H29" s="184">
+        <f t="shared" ref="H29:H31" si="4">_xlfn.XLOOKUP($E29,$D$17:$D$20,F$17:F$20,"該当なし")</f>
+        <v>1800</v>
+      </c>
+      <c r="I29" s="187">
+        <f t="shared" si="1"/>
+        <v>10800</v>
+      </c>
+      <c r="J29" s="187">
+        <f t="shared" ref="J29:J31" si="5">SUMIFS($G$8:$G$11,$E$8:$E$11,E29)</f>
+        <v>27000</v>
+      </c>
+      <c r="K29" s="179">
+        <f t="shared" si="2"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="30" spans="4:11" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="D30" s="104">
+        <v>4</v>
+      </c>
+      <c r="E30" s="178" t="s">
+        <v>269</v>
+      </c>
+      <c r="F30" s="178" t="str">
+        <f t="shared" si="0"/>
+        <v>地魚刺身盛</v>
+      </c>
+      <c r="G30" s="177">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="H30" s="184">
+        <f t="shared" si="4"/>
+        <v>1500</v>
+      </c>
+      <c r="I30" s="187">
+        <f t="shared" si="1"/>
+        <v>7500</v>
+      </c>
+      <c r="J30" s="187">
+        <f t="shared" si="5"/>
+        <v>19000</v>
+      </c>
+      <c r="K30" s="179">
+        <f t="shared" si="2"/>
+        <v>0.39473684210526316</v>
+      </c>
+    </row>
+    <row r="31" spans="4:11" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="D31" s="170">
+        <v>5</v>
+      </c>
+      <c r="E31" s="181" t="s">
+        <v>270</v>
+      </c>
+      <c r="F31" s="181" t="str">
+        <f>_xlfn.XLOOKUP($E31,$D$17:$D$20,E$17:E$20,"該当なし")</f>
+        <v>該当なし</v>
+      </c>
+      <c r="G31" s="180">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="H31" s="185" t="str">
+        <f t="shared" si="4"/>
+        <v>該当なし</v>
+      </c>
+      <c r="I31" s="188" t="str">
+        <f>IFERROR(G31*H31,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="J31" s="188">
+        <f t="shared" si="5"/>
+        <v>12000</v>
+      </c>
+      <c r="K31" s="182" t="str">
+        <f>IFERROR(I31/J31,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="11"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="B2:I33"/>
+  <dimension ref="B2:I31"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="2.36328125" customWidth="1"/>
@@ -4550,7 +5092,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="75" t="s">
+      <c r="B2" s="64" t="s">
         <v>88</v>
       </c>
     </row>
@@ -4561,53 +5103,53 @@
       </c>
     </row>
     <row r="5" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D5" s="77" t="s">
+      <c r="D5" s="66" t="s">
         <v>90</v>
       </c>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="H5" s="111" t="s">
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="H5" s="97" t="s">
         <v>240</v>
       </c>
-      <c r="I5" s="78"/>
+      <c r="I5" s="67"/>
     </row>
     <row r="6" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="7" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D7" s="79" t="s">
+      <c r="D7" s="68" t="s">
         <v>66</v>
       </c>
-      <c r="E7" s="79" t="s">
+      <c r="E7" s="68" t="s">
         <v>91</v>
       </c>
-      <c r="F7" s="79" t="s">
+      <c r="F7" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="H7" s="79" t="s">
+      <c r="H7" s="68" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="8" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D8" s="80" t="s">
+      <c r="D8" s="69" t="s">
         <v>70</v>
       </c>
-      <c r="E8" s="80" t="s">
+      <c r="E8" s="69" t="s">
         <v>93</v>
       </c>
-      <c r="F8" s="81">
+      <c r="F8" s="70">
         <v>160000</v>
       </c>
-      <c r="H8" s="112" t="s">
+      <c r="H8" s="98" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="9" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D9" s="83" t="s">
+      <c r="D9" s="72" t="s">
         <v>71</v>
       </c>
-      <c r="E9" s="83" t="s">
+      <c r="E9" s="72" t="s">
         <v>94</v>
       </c>
-      <c r="F9" s="84">
+      <c r="F9" s="73">
         <v>108000</v>
       </c>
       <c r="H9" s="3" t="s">
@@ -4615,13 +5157,13 @@
       </c>
     </row>
     <row r="10" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D10" s="83" t="s">
+      <c r="D10" s="72" t="s">
         <v>73</v>
       </c>
-      <c r="E10" s="83" t="s">
+      <c r="E10" s="72" t="s">
         <v>95</v>
       </c>
-      <c r="F10" s="84">
+      <c r="F10" s="73">
         <v>72000</v>
       </c>
       <c r="H10" s="3" t="s">
@@ -4629,200 +5171,203 @@
       </c>
     </row>
     <row r="11" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D11" s="83" t="s">
+      <c r="D11" s="72" t="s">
         <v>74</v>
       </c>
-      <c r="E11" s="83" t="s">
+      <c r="E11" s="72" t="s">
         <v>93</v>
       </c>
-      <c r="F11" s="84">
+      <c r="F11" s="73">
         <v>180000</v>
       </c>
     </row>
     <row r="12" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D12" s="83" t="s">
+      <c r="D12" s="72" t="s">
         <v>75</v>
       </c>
-      <c r="E12" s="83" t="s">
+      <c r="E12" s="72" t="s">
         <v>96</v>
       </c>
-      <c r="F12" s="84">
+      <c r="F12" s="73">
         <v>95000</v>
       </c>
     </row>
     <row r="13" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D13" s="83" t="s">
+      <c r="D13" s="72" t="s">
         <v>76</v>
       </c>
-      <c r="E13" s="83" t="s">
+      <c r="E13" s="72" t="s">
         <v>94</v>
       </c>
-      <c r="F13" s="84">
+      <c r="F13" s="73">
         <v>36000</v>
       </c>
     </row>
     <row r="14" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D14" s="83" t="s">
+      <c r="D14" s="72" t="s">
         <v>77</v>
       </c>
-      <c r="E14" s="83" t="s">
+      <c r="E14" s="72" t="s">
         <v>97</v>
       </c>
-      <c r="F14" s="84">
+      <c r="F14" s="73">
         <v>152000</v>
       </c>
+      <c r="H14" s="97" t="s">
+        <v>241</v>
+      </c>
+      <c r="I14" s="67"/>
     </row>
     <row r="15" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D15" s="83" t="s">
+      <c r="D15" s="72" t="s">
         <v>78</v>
       </c>
-      <c r="E15" s="83" t="s">
+      <c r="E15" s="72" t="s">
         <v>95</v>
       </c>
-      <c r="F15" s="84">
+      <c r="F15" s="73">
         <v>74000</v>
       </c>
     </row>
     <row r="16" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D16" s="83" t="s">
+      <c r="D16" s="72" t="s">
         <v>79</v>
       </c>
-      <c r="E16" s="83" t="s">
+      <c r="E16" s="72" t="s">
         <v>93</v>
       </c>
-      <c r="F16" s="84">
+      <c r="F16" s="73">
         <v>92000</v>
       </c>
+      <c r="H16" s="68" t="s">
+        <v>101</v>
+      </c>
+      <c r="I16" s="68" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="17" spans="4:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D17" s="83" t="s">
+      <c r="D17" s="72" t="s">
         <v>80</v>
       </c>
-      <c r="E17" s="83" t="s">
+      <c r="E17" s="72" t="s">
         <v>96</v>
       </c>
-      <c r="F17" s="84">
+      <c r="F17" s="73">
         <v>270000</v>
       </c>
+      <c r="H17" s="69" t="str" cm="1">
+        <f t="array" ref="H17:H22">_xlfn._xlws.SORT(_xlfn.UNIQUE(E8:E19))</f>
+        <v>Booking.com</v>
+      </c>
+      <c r="I17" s="70" cm="1">
+        <f t="array" ref="I17:I22">SUMIFS($F$8:$F$19,$E$8:$E$19,_xlfn.ANCHORARRAY(H17))</f>
+        <v>146000</v>
+      </c>
     </row>
     <row r="18" spans="4:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D18" s="83" t="s">
+      <c r="D18" s="72" t="s">
         <v>99</v>
       </c>
-      <c r="E18" s="83" t="s">
+      <c r="E18" s="72" t="s">
         <v>98</v>
       </c>
-      <c r="F18" s="84">
+      <c r="F18" s="73">
         <v>210000</v>
       </c>
+      <c r="H18" s="72" t="str">
+        <v>Expedia</v>
+      </c>
+      <c r="I18" s="73">
+        <v>152000</v>
+      </c>
     </row>
     <row r="19" spans="4:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D19" s="83" t="s">
+      <c r="D19" s="72" t="s">
         <v>100</v>
       </c>
-      <c r="E19" s="83" t="s">
+      <c r="E19" s="72" t="s">
         <v>94</v>
       </c>
-      <c r="F19" s="84">
+      <c r="F19" s="73">
         <v>64000</v>
       </c>
+      <c r="H19" s="72" t="str">
+        <v>じゃらん</v>
+      </c>
+      <c r="I19" s="73">
+        <v>208000</v>
+      </c>
     </row>
     <row r="20" spans="4:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D20" s="83"/>
-      <c r="E20" s="113" t="s">
+      <c r="D20" s="72"/>
+      <c r="E20" s="99" t="s">
         <v>245</v>
       </c>
-      <c r="F20" s="84"/>
+      <c r="F20" s="73"/>
+      <c r="H20" s="72" t="str">
+        <v>一休.com</v>
+      </c>
+      <c r="I20" s="73">
+        <v>210000</v>
+      </c>
     </row>
     <row r="21" spans="4:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D21" s="83"/>
-      <c r="E21" s="83"/>
-      <c r="F21" s="84"/>
+      <c r="D21" s="72"/>
+      <c r="E21" s="72"/>
+      <c r="F21" s="73"/>
+      <c r="H21" s="72" t="str">
+        <v>楽天トラベル</v>
+      </c>
+      <c r="I21" s="73">
+        <v>432000</v>
+      </c>
     </row>
     <row r="22" spans="4:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H22" s="111" t="s">
-        <v>241</v>
-      </c>
-      <c r="I22" s="78"/>
-    </row>
-    <row r="23" spans="4:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="D22" s="72"/>
+      <c r="E22" s="72"/>
+      <c r="F22" s="73"/>
+      <c r="H22" s="72" t="str">
+        <v>公式サイト</v>
+      </c>
+      <c r="I22" s="73">
+        <v>365000</v>
+      </c>
+    </row>
+    <row r="23" spans="4:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D23" s="72"/>
+      <c r="E23" s="72"/>
+      <c r="F23" s="73"/>
+      <c r="H23" s="72"/>
+      <c r="I23" s="73"/>
+    </row>
     <row r="24" spans="4:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H24" s="79" t="s">
-        <v>101</v>
-      </c>
-      <c r="I24" s="79" t="s">
-        <v>85</v>
-      </c>
+      <c r="D24" s="72"/>
+      <c r="E24" s="72"/>
+      <c r="F24" s="73"/>
+      <c r="H24" s="72"/>
+      <c r="I24" s="73"/>
     </row>
     <row r="25" spans="4:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H25" s="80" t="str" cm="1">
-        <f t="array" ref="H25:H30">_xlfn._xlws.SORT(_xlfn.UNIQUE(E8:E19))</f>
-        <v>Booking.com</v>
-      </c>
-      <c r="I25" s="81" cm="1">
-        <f t="array" ref="I25:I30">SUMIFS($F$8:$F$19,$E$8:$E$19,_xlfn.ANCHORARRAY(H25))</f>
-        <v>146000</v>
-      </c>
-    </row>
-    <row r="26" spans="4:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H26" s="83" t="str">
-        <v>Expedia</v>
-      </c>
-      <c r="I26" s="84">
-        <v>152000</v>
-      </c>
-    </row>
-    <row r="27" spans="4:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H27" s="83" t="str">
-        <v>じゃらん</v>
-      </c>
-      <c r="I27" s="84">
-        <v>208000</v>
-      </c>
-    </row>
-    <row r="28" spans="4:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H28" s="83" t="str">
-        <v>一休.com</v>
-      </c>
-      <c r="I28" s="84">
-        <v>210000</v>
-      </c>
-    </row>
-    <row r="29" spans="4:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H29" s="83" t="str">
-        <v>楽天トラベル</v>
-      </c>
-      <c r="I29" s="84">
-        <v>432000</v>
-      </c>
-    </row>
-    <row r="30" spans="4:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H30" s="83" t="str">
-        <v>公式サイト</v>
-      </c>
-      <c r="I30" s="84">
-        <v>365000</v>
-      </c>
-    </row>
-    <row r="31" spans="4:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H31" s="83"/>
-      <c r="I31" s="84"/>
-    </row>
-    <row r="32" spans="4:9" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="H32" s="83"/>
-      <c r="I32" s="84"/>
-    </row>
-    <row r="33" spans="8:9" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="H33" s="83"/>
-      <c r="I33" s="84"/>
-    </row>
+      <c r="D25" s="72"/>
+      <c r="E25" s="72"/>
+      <c r="F25" s="73"/>
+      <c r="H25" s="72"/>
+      <c r="I25" s="73"/>
+    </row>
+    <row r="26" spans="4:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="4:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="4:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="4:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="4:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="4:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <phoneticPr fontId="11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B2:F25"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
@@ -4834,7 +5379,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="75" t="s">
+      <c r="B2" s="64" t="s">
         <v>102</v>
       </c>
     </row>
@@ -4845,85 +5390,85 @@
       </c>
     </row>
     <row r="5" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D5" s="77" t="s">
+      <c r="D5" s="66" t="s">
         <v>104</v>
       </c>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
     </row>
     <row r="6" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="7" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D7" s="79" t="s">
+      <c r="D7" s="68" t="s">
         <v>105</v>
       </c>
-      <c r="E7" s="79" t="s">
+      <c r="E7" s="68" t="s">
         <v>106</v>
       </c>
-      <c r="F7" s="79" t="s">
+      <c r="F7" s="68" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="8" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D8" s="80" t="s">
+      <c r="D8" s="69" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="87">
+      <c r="E8" s="76">
         <v>20</v>
       </c>
-      <c r="F8" s="88" t="s">
+      <c r="F8" s="77" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="9" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D9" s="83" t="s">
+      <c r="D9" s="72" t="s">
         <v>109</v>
       </c>
-      <c r="E9" s="89">
+      <c r="E9" s="78">
         <v>365</v>
       </c>
-      <c r="F9" s="90" t="s">
+      <c r="F9" s="79" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="10" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D10" s="83" t="s">
+      <c r="D10" s="72" t="s">
         <v>5</v>
       </c>
-      <c r="E10" s="91">
+      <c r="E10" s="80">
         <v>0.65</v>
       </c>
-      <c r="F10" s="90"/>
+      <c r="F10" s="79"/>
     </row>
     <row r="11" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D11" s="83" t="s">
+      <c r="D11" s="72" t="s">
         <v>111</v>
       </c>
-      <c r="E11" s="89">
+      <c r="E11" s="78">
         <v>50000</v>
       </c>
-      <c r="F11" s="90" t="s">
+      <c r="F11" s="79" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="12" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D12" s="83" t="s">
+      <c r="D12" s="72" t="s">
         <v>113</v>
       </c>
-      <c r="E12" s="92">
+      <c r="E12" s="81">
         <v>2</v>
       </c>
-      <c r="F12" s="90" t="s">
+      <c r="F12" s="79" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="13" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D13" s="85" t="s">
+      <c r="D13" s="74" t="s">
         <v>115</v>
       </c>
-      <c r="E13" s="93">
+      <c r="E13" s="82">
         <v>6000</v>
       </c>
-      <c r="F13" s="94" t="s">
+      <c r="F13" s="83" t="s">
         <v>112</v>
       </c>
     </row>
@@ -4931,52 +5476,52 @@
     <row r="15" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="16" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="17" spans="4:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D17" s="111" t="s">
+      <c r="D17" s="97" t="s">
         <v>256</v>
       </c>
-      <c r="E17" s="78"/>
-      <c r="F17" s="78"/>
+      <c r="E17" s="67"/>
+      <c r="F17" s="67"/>
     </row>
     <row r="18" spans="4:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="19" spans="4:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D19" s="79" t="s">
+      <c r="D19" s="68" t="s">
         <v>105</v>
       </c>
-      <c r="E19" s="79" t="s">
+      <c r="E19" s="68" t="s">
         <v>106</v>
       </c>
-      <c r="F19" s="79" t="s">
+      <c r="F19" s="68" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="20" spans="4:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D20" s="80" t="s">
+      <c r="D20" s="69" t="s">
         <v>116</v>
       </c>
-      <c r="E20" s="95">
+      <c r="E20" s="84">
         <v>0.3</v>
       </c>
-      <c r="F20" s="88"/>
+      <c r="F20" s="77"/>
     </row>
     <row r="21" spans="4:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D21" s="83" t="s">
+      <c r="D21" s="72" t="s">
         <v>117</v>
       </c>
-      <c r="E21" s="89">
+      <c r="E21" s="78">
         <v>60000000</v>
       </c>
-      <c r="F21" s="90" t="s">
+      <c r="F21" s="79" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="22" spans="4:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D22" s="85" t="s">
+      <c r="D22" s="74" t="s">
         <v>118</v>
       </c>
-      <c r="E22" s="93">
+      <c r="E22" s="82">
         <v>48000000</v>
       </c>
-      <c r="F22" s="94" t="s">
+      <c r="F22" s="83" t="s">
         <v>112</v>
       </c>
     </row>
@@ -4993,7 +5538,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B2:F34"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
@@ -5005,7 +5550,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="75" t="s">
+      <c r="B2" s="64" t="s">
         <v>120</v>
       </c>
     </row>
@@ -5016,255 +5561,251 @@
       </c>
     </row>
     <row r="5" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D5" s="77" t="s">
+      <c r="D5" s="66" t="s">
         <v>121</v>
       </c>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
     </row>
     <row r="6" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="7" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D7" s="79" t="s">
+      <c r="D7" s="68" t="s">
         <v>105</v>
       </c>
-      <c r="E7" s="79" t="s">
+      <c r="E7" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="F7" s="79" t="s">
+      <c r="F7" s="68" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="8" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D8" s="115" t="s">
+      <c r="D8" s="101" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="114">
+      <c r="E8" s="100">
         <f>'2-4_PL①Input'!E8</f>
         <v>20</v>
       </c>
-      <c r="F8" s="115" t="s">
+      <c r="F8" s="101" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="9" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D9" s="118" t="s">
+      <c r="D9" s="104" t="s">
         <v>109</v>
       </c>
-      <c r="E9" s="119">
+      <c r="E9" s="105">
         <f>'2-4_PL①Input'!E9</f>
         <v>365</v>
       </c>
-      <c r="F9" s="118" t="s">
+      <c r="F9" s="104" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="10" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D10" s="120" t="s">
+      <c r="D10" s="106" t="s">
         <v>5</v>
       </c>
-      <c r="E10" s="121">
+      <c r="E10" s="107">
         <f>'2-4_PL①Input'!E10</f>
         <v>0.65</v>
       </c>
-      <c r="F10" s="120" t="s">
+      <c r="F10" s="106" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="11" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D11" s="127" t="s">
+      <c r="D11" s="112" t="s">
         <v>248</v>
       </c>
-      <c r="E11" s="135">
+      <c r="E11" s="119">
         <f>E8*E9*E10</f>
         <v>4745</v>
       </c>
-      <c r="F11" s="128" t="s">
+      <c r="F11" s="113" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D12" s="134"/>
-      <c r="E12" s="134"/>
-      <c r="F12" s="134"/>
-    </row>
+    <row r="12" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="13" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D13" s="130" t="str">
+      <c r="D13" s="115" t="str">
         <f>'2-4_PL①Input'!$D$11</f>
         <v>ADR（客室単価）</v>
       </c>
-      <c r="E13" s="131">
+      <c r="E13" s="116">
         <f>'2-4_PL①Input'!E11</f>
         <v>50000</v>
       </c>
-      <c r="F13" s="82" t="s">
+      <c r="F13" s="71" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="14" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D14" s="124" t="s">
+      <c r="D14" s="109" t="s">
         <v>124</v>
       </c>
-      <c r="E14" s="136">
+      <c r="E14" s="120">
         <f>E11*E13</f>
         <v>237250000</v>
       </c>
-      <c r="F14" s="124" t="s">
+      <c r="F14" s="109" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="15" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D15" s="124"/>
-      <c r="E15" s="136"/>
-      <c r="F15" s="124"/>
+      <c r="D15" s="109"/>
+      <c r="E15" s="120"/>
+      <c r="F15" s="109"/>
     </row>
     <row r="16" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D16" s="116" t="s">
+      <c r="D16" s="102" t="s">
         <v>249</v>
       </c>
-      <c r="E16" s="138">
+      <c r="E16" s="122">
         <f>'2-4_PL①Input'!E12</f>
         <v>2</v>
       </c>
-      <c r="F16" s="80" t="s">
+      <c r="F16" s="69" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="17" spans="4:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D17" s="132" t="str">
+      <c r="D17" s="117" t="str">
         <f>'2-4_PL①Input'!$D$13</f>
         <v>飲食単価/人</v>
       </c>
-      <c r="E17" s="133">
+      <c r="E17" s="118">
         <f>'2-4_PL①Input'!E13</f>
         <v>6000</v>
       </c>
-      <c r="F17" s="85" t="s">
+      <c r="F17" s="74" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="18" spans="4:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D18" s="124" t="s">
+      <c r="D18" s="109" t="s">
         <v>126</v>
       </c>
-      <c r="E18" s="136">
+      <c r="E18" s="120">
         <f>E11*E16*E17</f>
         <v>56940000</v>
       </c>
-      <c r="F18" s="122" t="s">
+      <c r="F18" s="7" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="19" spans="4:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D19" s="124"/>
-      <c r="E19" s="136"/>
-      <c r="F19" s="124"/>
+      <c r="D19" s="109"/>
+      <c r="E19" s="120"/>
+      <c r="F19" s="109"/>
     </row>
     <row r="20" spans="4:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D20" s="143" t="s">
+      <c r="D20" s="127" t="s">
         <v>127</v>
       </c>
-      <c r="E20" s="144">
+      <c r="E20" s="128">
         <f>E14+E18</f>
         <v>294190000</v>
       </c>
-      <c r="F20" s="145" t="s">
+      <c r="F20" s="129" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="21" spans="4:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D21" s="124"/>
-      <c r="E21" s="124"/>
-      <c r="F21" s="124"/>
+      <c r="D21" s="109"/>
+      <c r="E21" s="109"/>
+      <c r="F21" s="109"/>
     </row>
     <row r="22" spans="4:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D22" s="122" t="s">
+      <c r="D22" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="E22" s="117">
+      <c r="E22" s="103">
         <f>'2-4_PL①Input'!E20</f>
         <v>0.3</v>
       </c>
-      <c r="F22" s="124" t="s">
+      <c r="F22" s="109" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="23" spans="4:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D23" s="124" t="s">
+      <c r="D23" s="109" t="s">
         <v>129</v>
       </c>
-      <c r="E23" s="136">
+      <c r="E23" s="120">
         <f>E20*E22</f>
         <v>88257000</v>
       </c>
-      <c r="F23" s="124" t="s">
+      <c r="F23" s="109" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="24" spans="4:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D24" s="146" t="s">
+      <c r="D24" s="130" t="s">
         <v>131</v>
       </c>
-      <c r="E24" s="147">
+      <c r="E24" s="131">
         <f>E20-E23</f>
         <v>205933000</v>
       </c>
-      <c r="F24" s="148" t="s">
+      <c r="F24" s="132" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="25" spans="4:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D25" s="124"/>
-      <c r="E25" s="140"/>
-      <c r="F25" s="124"/>
+      <c r="D25" s="109"/>
+      <c r="E25" s="124"/>
+      <c r="F25" s="109"/>
     </row>
     <row r="26" spans="4:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D26" s="80" t="str">
+      <c r="D26" s="69" t="str">
         <f>'2-4_PL①Input'!D21</f>
         <v>人件費（固定・年）</v>
       </c>
-      <c r="E26" s="114">
+      <c r="E26" s="100">
         <f>'2-4_PL①Input'!E21</f>
         <v>60000000</v>
       </c>
-      <c r="F26" s="80"/>
+      <c r="F26" s="69"/>
     </row>
     <row r="27" spans="4:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D27" s="85" t="str">
+      <c r="D27" s="74" t="str">
         <f>'2-4_PL①Input'!D22</f>
         <v>その他固定費（年）</v>
       </c>
-      <c r="E27" s="142">
+      <c r="E27" s="126">
         <f>'2-4_PL①Input'!E22</f>
         <v>48000000</v>
       </c>
-      <c r="F27" s="85"/>
+      <c r="F27" s="74"/>
     </row>
     <row r="28" spans="4:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D28" s="151" t="s">
+      <c r="D28" s="135" t="s">
         <v>133</v>
       </c>
-      <c r="E28" s="152">
+      <c r="E28" s="136">
         <f>SUM(E26:E27)</f>
         <v>108000000</v>
       </c>
-      <c r="F28" s="153" t="s">
+      <c r="F28" s="137" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="29" spans="4:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D29" s="124"/>
-      <c r="E29" s="136"/>
-      <c r="F29" s="124"/>
+      <c r="D29" s="109"/>
+      <c r="E29" s="120"/>
+      <c r="F29" s="109"/>
     </row>
     <row r="30" spans="4:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D30" s="143" t="s">
+      <c r="D30" s="127" t="s">
         <v>135</v>
       </c>
-      <c r="E30" s="149">
+      <c r="E30" s="133">
         <f>E24-E28</f>
         <v>97933000</v>
       </c>
-      <c r="F30" s="150" t="s">
+      <c r="F30" s="134" t="s">
         <v>136</v>
       </c>
     </row>
@@ -5282,7 +5823,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="B2:F19"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
@@ -5294,7 +5835,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="75" t="s">
+      <c r="B2" s="64" t="s">
         <v>138</v>
       </c>
     </row>
@@ -5305,100 +5846,92 @@
       </c>
     </row>
     <row r="5" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D5" s="77" t="s">
+      <c r="D5" s="66" t="s">
         <v>139</v>
       </c>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
     </row>
     <row r="6" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D6" s="165" t="s">
+      <c r="D6" s="145" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="8" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D8" s="79" t="s">
+      <c r="D8" s="68" t="s">
         <v>105</v>
       </c>
-      <c r="E8" s="154" t="s">
+      <c r="E8" s="138" t="s">
         <v>255</v>
       </c>
-      <c r="F8" s="154" t="s">
+      <c r="F8" s="138" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="9" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D9" s="128" t="s">
+      <c r="D9" s="113" t="s">
         <v>140</v>
       </c>
-      <c r="E9" s="155">
+      <c r="E9" s="139">
         <f>'2-4_PL②計算'!E20/10^6</f>
         <v>294.19</v>
       </c>
-      <c r="F9" s="156">
+      <c r="F9" s="140">
         <f>E9/$E$9</f>
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D10" s="134"/>
-      <c r="E10" s="134"/>
-      <c r="F10" s="134"/>
-    </row>
+    <row r="10" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="11" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D11" s="129" t="s">
+      <c r="D11" s="114" t="s">
         <v>257</v>
       </c>
-      <c r="E11" s="137">
+      <c r="E11" s="121">
         <f>'2-4_PL②計算'!E23/10^6</f>
         <v>88.257000000000005</v>
       </c>
-      <c r="F11" s="157">
+      <c r="F11" s="141">
         <f>-E11/$E$9</f>
         <v>-0.30000000000000004</v>
       </c>
     </row>
     <row r="12" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D12" s="127" t="s">
+      <c r="D12" s="112" t="s">
         <v>131</v>
       </c>
-      <c r="E12" s="161">
+      <c r="E12" s="139">
         <f>E9-E11</f>
         <v>205.93299999999999</v>
       </c>
-      <c r="F12" s="162">
+      <c r="F12" s="142">
         <f>E12/$E$9</f>
         <v>0.7</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D13" s="134"/>
-      <c r="E13" s="158"/>
-      <c r="F13" s="158"/>
-    </row>
+    <row r="13" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="14" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D14" s="129" t="s">
+      <c r="D14" s="114" t="s">
         <v>258</v>
       </c>
-      <c r="E14" s="159">
+      <c r="E14" s="121">
         <f>'2-4_PL②計算'!E28/10^6</f>
         <v>108</v>
       </c>
-      <c r="F14" s="160">
+      <c r="F14" s="141">
         <f>-E14/$E$9</f>
         <v>-0.36710969101601004</v>
       </c>
     </row>
     <row r="15" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D15" s="143" t="s">
+      <c r="D15" s="127" t="s">
         <v>135</v>
       </c>
-      <c r="E15" s="163">
+      <c r="E15" s="143">
         <f>E12-E14</f>
         <v>97.932999999999993</v>
       </c>
-      <c r="F15" s="164">
+      <c r="F15" s="144">
         <f>E15/$E$9</f>
         <v>0.33289030898398991</v>
       </c>
@@ -5417,7 +5950,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="B2:F25"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
@@ -5429,7 +5962,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="75" t="s">
+      <c r="B2" s="64" t="s">
         <v>142</v>
       </c>
     </row>
@@ -5440,54 +5973,54 @@
       </c>
     </row>
     <row r="5" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D5" s="77" t="s">
+      <c r="D5" s="66" t="s">
         <v>144</v>
       </c>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
     </row>
     <row r="6" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="7" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D7" s="79" t="s">
+      <c r="D7" s="68" t="s">
         <v>105</v>
       </c>
-      <c r="E7" s="79" t="s">
+      <c r="E7" s="68" t="s">
         <v>145</v>
       </c>
-      <c r="F7" s="79" t="s">
+      <c r="F7" s="68" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="8" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D8" s="80" t="s">
+      <c r="D8" s="69" t="s">
         <v>147</v>
       </c>
-      <c r="E8" s="80" t="s">
+      <c r="E8" s="69" t="s">
         <v>148</v>
       </c>
-      <c r="F8" s="88" t="s">
+      <c r="F8" s="77" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="9" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D9" s="83" t="s">
+      <c r="D9" s="72" t="s">
         <v>150</v>
       </c>
-      <c r="E9" s="83" t="s">
+      <c r="E9" s="72" t="s">
         <v>151</v>
       </c>
-      <c r="F9" s="90" t="s">
+      <c r="F9" s="79" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="10" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D10" s="85" t="s">
+      <c r="D10" s="74" t="s">
         <v>152</v>
       </c>
-      <c r="E10" s="85" t="s">
+      <c r="E10" s="74" t="s">
         <v>153</v>
       </c>
-      <c r="F10" s="94" t="s">
+      <c r="F10" s="83" t="s">
         <v>149</v>
       </c>
     </row>
@@ -5495,98 +6028,98 @@
     <row r="12" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="13" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="14" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D14" s="77" t="s">
+      <c r="D14" s="66" t="s">
         <v>154</v>
       </c>
-      <c r="E14" s="78"/>
-      <c r="F14" s="78"/>
+      <c r="E14" s="67"/>
+      <c r="F14" s="67"/>
     </row>
     <row r="15" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="16" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D16" s="79" t="s">
+      <c r="D16" s="68" t="s">
         <v>155</v>
       </c>
-      <c r="E16" s="79" t="s">
+      <c r="E16" s="68" t="s">
         <v>156</v>
       </c>
-      <c r="F16" s="79" t="s">
+      <c r="F16" s="68" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="17" spans="4:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D17" s="80" t="s">
+      <c r="D17" s="69" t="s">
         <v>158</v>
       </c>
-      <c r="E17" s="80" t="s">
+      <c r="E17" s="69" t="s">
         <v>159</v>
       </c>
-      <c r="F17" s="88" t="s">
+      <c r="F17" s="77" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="18" spans="4:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D18" s="83" t="s">
+      <c r="D18" s="72" t="s">
         <v>161</v>
       </c>
-      <c r="E18" s="83" t="s">
+      <c r="E18" s="72" t="s">
         <v>162</v>
       </c>
-      <c r="F18" s="90" t="s">
+      <c r="F18" s="79" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="19" spans="4:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D19" s="83" t="s">
+      <c r="D19" s="72" t="s">
         <v>164</v>
       </c>
-      <c r="E19" s="83" t="s">
+      <c r="E19" s="72" t="s">
         <v>165</v>
       </c>
-      <c r="F19" s="90" t="s">
+      <c r="F19" s="79" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="20" spans="4:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D20" s="83" t="s">
+      <c r="D20" s="72" t="s">
         <v>167</v>
       </c>
-      <c r="E20" s="83" t="s">
+      <c r="E20" s="72" t="s">
         <v>168</v>
       </c>
-      <c r="F20" s="90" t="s">
+      <c r="F20" s="79" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="21" spans="4:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D21" s="83" t="s">
+      <c r="D21" s="72" t="s">
         <v>170</v>
       </c>
-      <c r="E21" s="83" t="s">
+      <c r="E21" s="72" t="s">
         <v>171</v>
       </c>
-      <c r="F21" s="90" t="s">
+      <c r="F21" s="79" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="22" spans="4:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D22" s="83" t="s">
+      <c r="D22" s="72" t="s">
         <v>173</v>
       </c>
-      <c r="E22" s="83" t="s">
+      <c r="E22" s="72" t="s">
         <v>174</v>
       </c>
-      <c r="F22" s="90" t="s">
+      <c r="F22" s="79" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="23" spans="4:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D23" s="85" t="s">
+      <c r="D23" s="74" t="s">
         <v>176</v>
       </c>
-      <c r="E23" s="85" t="s">
+      <c r="E23" s="74" t="s">
         <v>177</v>
       </c>
-      <c r="F23" s="94" t="s">
+      <c r="F23" s="83" t="s">
         <v>178</v>
       </c>
     </row>
@@ -5596,89 +6129,4 @@
   <phoneticPr fontId="11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="B2:F13"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="3" width="2.36328125" customWidth="1"/>
-    <col min="4" max="4" width="15.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="10" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="75" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="3" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="5" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D5" s="77" t="s">
-        <v>180</v>
-      </c>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-    </row>
-    <row r="6" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="7" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D7" s="79" t="s">
-        <v>105</v>
-      </c>
-      <c r="E7" s="79" t="s">
-        <v>106</v>
-      </c>
-      <c r="F7" s="79" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D8" s="124" t="s">
-        <v>150</v>
-      </c>
-      <c r="E8" s="187">
-        <v>0.1</v>
-      </c>
-      <c r="F8" s="168"/>
-    </row>
-    <row r="9" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D9" s="124" t="s">
-        <v>181</v>
-      </c>
-      <c r="E9" s="188">
-        <v>7</v>
-      </c>
-      <c r="F9" s="168" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D10" s="124" t="s">
-        <v>182</v>
-      </c>
-      <c r="E10" s="188">
-        <v>8</v>
-      </c>
-      <c r="F10" s="168" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D11" s="124" t="s">
-        <v>183</v>
-      </c>
-      <c r="E11" s="187">
-        <v>0.7</v>
-      </c>
-      <c r="F11" s="168"/>
-    </row>
-    <row r="12" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="13" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-  </sheetData>
-  <phoneticPr fontId="11"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/files/excel-mastery-full.xlsx
+++ b/files/excel-mastery-full.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Mac\Home\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D75F65E6-DCB5-4F65-A249-F4C3B5449CC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F09D7E25-B815-4580-BF69-898C15D10CFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1605" yWindow="-16320" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="280" windowWidth="17320" windowHeight="10400" tabRatio="773" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-1_体裁の対比" sheetId="1" r:id="rId1"/>
     <sheet name="1-2_操作イメージ" sheetId="2" r:id="rId2"/>
     <sheet name="2-1_実績集計_SUMIFS" sheetId="3" r:id="rId3"/>
     <sheet name="2-1_実績集計_XLOOKUP" sheetId="17" r:id="rId4"/>
-    <sheet name="2-2_クリーニング" sheetId="4" r:id="rId5"/>
+    <sheet name="2-2_クリーニング_スピル関数" sheetId="4" r:id="rId5"/>
     <sheet name="2-4_PL①Input" sheetId="5" r:id="rId6"/>
     <sheet name="2-4_PL②計算" sheetId="6" r:id="rId7"/>
     <sheet name="2-4_PL③Output" sheetId="7" r:id="rId8"/>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="286">
   <si>
     <t>1-1. 体裁を統一できる ― 良い例と悪い例の対比</t>
   </si>
@@ -815,10 +815,6 @@
     <rPh sb="2" eb="4">
       <t>ジツレイ</t>
     </rPh>
-    <phoneticPr fontId="11"/>
-  </si>
-  <si>
-    <t>=SORT(UNIQUE(...))</t>
     <phoneticPr fontId="11"/>
   </si>
   <si>
@@ -1036,6 +1032,34 @@
     <rPh sb="11" eb="14">
       <t>ゲンカリツ</t>
     </rPh>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>海外/国内</t>
+    <rPh sb="0" eb="2">
+      <t>カイガイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コクナイ</t>
+    </rPh>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>国内</t>
+    <rPh sb="0" eb="2">
+      <t>コクナイ</t>
+    </rPh>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>海外</t>
+    <rPh sb="0" eb="2">
+      <t>カイガイ</t>
+    </rPh>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>=SORT(UNIQUE(FILTER(#:#,#:#=***)))</t>
     <phoneticPr fontId="11"/>
   </si>
 </sst>
@@ -1570,7 +1594,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="191">
+  <cellXfs count="192">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2066,74 +2090,77 @@
     <xf numFmtId="3" fontId="23" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="9" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="9" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="パーセント" xfId="3" builtinId="5"/>
@@ -2768,13 +2795,13 @@
       </c>
     </row>
     <row r="25" spans="3:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D25" s="167" t="s">
+      <c r="D25" s="189" t="s">
         <v>11</v>
       </c>
-      <c r="E25" s="168"/>
-      <c r="F25" s="168"/>
-      <c r="G25" s="168"/>
-      <c r="H25" s="169"/>
+      <c r="E25" s="190"/>
+      <c r="F25" s="190"/>
+      <c r="G25" s="190"/>
+      <c r="H25" s="191"/>
       <c r="I25" s="42" t="e">
         <f>SUM(I22:I24)</f>
         <v>#VALUE!</v>
@@ -3292,7 +3319,7 @@
         <v>85</v>
       </c>
       <c r="F7" s="138" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G7" s="68" t="s">
         <v>3</v>
@@ -4307,255 +4334,255 @@
       <c r="D6" s="2"/>
     </row>
     <row r="7" spans="2:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D7" s="171" t="s">
+      <c r="D7" s="168" t="s">
         <v>66</v>
       </c>
-      <c r="E7" s="171" t="s">
+      <c r="E7" s="168" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="171" t="s">
+      <c r="F7" s="168" t="s">
         <v>47</v>
       </c>
-      <c r="G7" s="171" t="s">
+      <c r="G7" s="168" t="s">
         <v>67</v>
       </c>
-      <c r="H7" s="171" t="s">
+      <c r="H7" s="168" t="s">
         <v>68</v>
       </c>
-      <c r="I7" s="171" t="s">
+      <c r="I7" s="168" t="s">
         <v>69</v>
       </c>
-      <c r="J7" s="171" t="s">
+      <c r="J7" s="168" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="8" spans="2:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D8" s="172" t="s">
+      <c r="D8" s="169" t="s">
         <v>70</v>
       </c>
-      <c r="E8" s="172" t="s">
+      <c r="E8" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="189">
+      <c r="F8" s="186">
         <v>7</v>
       </c>
-      <c r="G8" s="172" t="s">
+      <c r="G8" s="169" t="s">
         <v>61</v>
       </c>
-      <c r="H8" s="173">
+      <c r="H8" s="170">
         <v>2</v>
       </c>
-      <c r="I8" s="173">
+      <c r="I8" s="170">
         <v>4</v>
       </c>
-      <c r="J8" s="173">
+      <c r="J8" s="170">
         <v>160000</v>
       </c>
     </row>
     <row r="9" spans="2:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D9" s="172" t="s">
+      <c r="D9" s="169" t="s">
         <v>71</v>
       </c>
-      <c r="E9" s="172" t="s">
+      <c r="E9" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="189">
+      <c r="F9" s="186">
         <v>7</v>
       </c>
-      <c r="G9" s="172" t="s">
+      <c r="G9" s="169" t="s">
         <v>72</v>
       </c>
-      <c r="H9" s="173">
+      <c r="H9" s="170">
         <v>3</v>
       </c>
-      <c r="I9" s="173">
+      <c r="I9" s="170">
         <v>4</v>
       </c>
-      <c r="J9" s="173">
+      <c r="J9" s="170">
         <v>108000</v>
       </c>
     </row>
     <row r="10" spans="2:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D10" s="172" t="s">
+      <c r="D10" s="169" t="s">
         <v>73</v>
       </c>
-      <c r="E10" s="172" t="s">
+      <c r="E10" s="169" t="s">
         <v>9</v>
       </c>
-      <c r="F10" s="189">
+      <c r="F10" s="186">
         <v>7</v>
       </c>
-      <c r="G10" s="172" t="s">
+      <c r="G10" s="169" t="s">
         <v>72</v>
       </c>
-      <c r="H10" s="173">
+      <c r="H10" s="170">
         <v>2</v>
       </c>
-      <c r="I10" s="173">
+      <c r="I10" s="170">
         <v>3</v>
       </c>
-      <c r="J10" s="173">
+      <c r="J10" s="170">
         <v>72000</v>
       </c>
     </row>
     <row r="11" spans="2:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D11" s="172" t="s">
+      <c r="D11" s="169" t="s">
         <v>74</v>
       </c>
-      <c r="E11" s="172" t="s">
+      <c r="E11" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="189">
+      <c r="F11" s="186">
         <v>8</v>
       </c>
-      <c r="G11" s="172" t="s">
+      <c r="G11" s="169" t="s">
         <v>61</v>
       </c>
-      <c r="H11" s="173">
+      <c r="H11" s="170">
         <v>2</v>
       </c>
-      <c r="I11" s="173">
+      <c r="I11" s="170">
         <v>2</v>
       </c>
-      <c r="J11" s="173">
+      <c r="J11" s="170">
         <v>180000</v>
       </c>
     </row>
     <row r="12" spans="2:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D12" s="172" t="s">
+      <c r="D12" s="169" t="s">
         <v>75</v>
       </c>
-      <c r="E12" s="172" t="s">
+      <c r="E12" s="169" t="s">
         <v>9</v>
       </c>
-      <c r="F12" s="189">
+      <c r="F12" s="186">
         <v>8</v>
       </c>
-      <c r="G12" s="172" t="s">
+      <c r="G12" s="169" t="s">
         <v>61</v>
       </c>
-      <c r="H12" s="173">
+      <c r="H12" s="170">
         <v>1</v>
       </c>
-      <c r="I12" s="173">
+      <c r="I12" s="170">
         <v>2</v>
       </c>
-      <c r="J12" s="173">
+      <c r="J12" s="170">
         <v>95000</v>
       </c>
     </row>
     <row r="13" spans="2:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D13" s="172" t="s">
+      <c r="D13" s="169" t="s">
         <v>76</v>
       </c>
-      <c r="E13" s="172" t="s">
+      <c r="E13" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="F13" s="189">
+      <c r="F13" s="186">
         <v>7</v>
       </c>
-      <c r="G13" s="172" t="s">
+      <c r="G13" s="169" t="s">
         <v>72</v>
       </c>
-      <c r="H13" s="173">
+      <c r="H13" s="170">
         <v>1</v>
       </c>
-      <c r="I13" s="173">
+      <c r="I13" s="170">
         <v>2</v>
       </c>
-      <c r="J13" s="173">
+      <c r="J13" s="170">
         <v>36000</v>
       </c>
     </row>
     <row r="14" spans="2:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D14" s="172" t="s">
+      <c r="D14" s="169" t="s">
         <v>77</v>
       </c>
-      <c r="E14" s="172" t="s">
+      <c r="E14" s="169" t="s">
         <v>9</v>
       </c>
-      <c r="F14" s="189">
+      <c r="F14" s="186">
         <v>8</v>
       </c>
-      <c r="G14" s="172" t="s">
+      <c r="G14" s="169" t="s">
         <v>72</v>
       </c>
-      <c r="H14" s="173">
+      <c r="H14" s="170">
         <v>4</v>
       </c>
-      <c r="I14" s="173">
+      <c r="I14" s="170">
         <v>6</v>
       </c>
-      <c r="J14" s="173">
+      <c r="J14" s="170">
         <v>152000</v>
       </c>
     </row>
     <row r="15" spans="2:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D15" s="172" t="s">
+      <c r="D15" s="169" t="s">
         <v>78</v>
       </c>
-      <c r="E15" s="172" t="s">
+      <c r="E15" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="189">
+      <c r="F15" s="186">
         <v>8</v>
       </c>
-      <c r="G15" s="172" t="s">
+      <c r="G15" s="169" t="s">
         <v>72</v>
       </c>
-      <c r="H15" s="173">
+      <c r="H15" s="170">
         <v>2</v>
       </c>
-      <c r="I15" s="173">
+      <c r="I15" s="170">
         <v>3</v>
       </c>
-      <c r="J15" s="173">
+      <c r="J15" s="170">
         <v>74000</v>
       </c>
     </row>
     <row r="16" spans="2:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D16" s="172" t="s">
+      <c r="D16" s="169" t="s">
         <v>79</v>
       </c>
-      <c r="E16" s="172" t="s">
+      <c r="E16" s="169" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="189">
+      <c r="F16" s="186">
         <v>7</v>
       </c>
-      <c r="G16" s="172" t="s">
+      <c r="G16" s="169" t="s">
         <v>61</v>
       </c>
-      <c r="H16" s="173">
+      <c r="H16" s="170">
         <v>1</v>
       </c>
-      <c r="I16" s="173">
+      <c r="I16" s="170">
         <v>2</v>
       </c>
-      <c r="J16" s="173">
+      <c r="J16" s="170">
         <v>92000</v>
       </c>
     </row>
     <row r="17" spans="3:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D17" s="172" t="s">
+      <c r="D17" s="169" t="s">
         <v>80</v>
       </c>
-      <c r="E17" s="172" t="s">
+      <c r="E17" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="F17" s="189">
+      <c r="F17" s="186">
         <v>8</v>
       </c>
-      <c r="G17" s="172" t="s">
+      <c r="G17" s="169" t="s">
         <v>61</v>
       </c>
-      <c r="H17" s="173">
+      <c r="H17" s="170">
         <v>3</v>
       </c>
-      <c r="I17" s="173">
+      <c r="I17" s="170">
         <v>5</v>
       </c>
-      <c r="J17" s="173">
+      <c r="J17" s="170">
         <v>270000</v>
       </c>
     </row>
@@ -4743,7 +4770,7 @@
   <sheetData>
     <row r="2" spans="2:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C2" s="1"/>
     </row>
@@ -4773,79 +4800,79 @@
       <c r="D6" s="2"/>
     </row>
     <row r="7" spans="2:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D7" s="171" t="s">
+      <c r="D7" s="168" t="s">
+        <v>261</v>
+      </c>
+      <c r="E7" s="168" t="s">
         <v>262</v>
       </c>
-      <c r="E7" s="171" t="s">
-        <v>263</v>
-      </c>
-      <c r="F7" s="171" t="s">
+      <c r="F7" s="168" t="s">
+        <v>264</v>
+      </c>
+      <c r="G7" s="168" t="s">
         <v>265</v>
       </c>
-      <c r="G7" s="171" t="s">
+    </row>
+    <row r="8" spans="2:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D8" s="169">
+        <v>2</v>
+      </c>
+      <c r="E8" s="169" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="8" spans="2:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D8" s="172">
+      <c r="F8" s="169">
+        <v>4</v>
+      </c>
+      <c r="G8" s="170">
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D9" s="169">
+        <v>3</v>
+      </c>
+      <c r="E9" s="169" t="s">
+        <v>267</v>
+      </c>
+      <c r="F9" s="169">
+        <v>6</v>
+      </c>
+      <c r="G9" s="170">
+        <v>27000</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D10" s="169">
+        <v>4</v>
+      </c>
+      <c r="E10" s="169" t="s">
+        <v>268</v>
+      </c>
+      <c r="F10" s="169">
+        <v>5</v>
+      </c>
+      <c r="G10" s="170">
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D11" s="169">
+        <v>5</v>
+      </c>
+      <c r="E11" s="169" t="s">
+        <v>269</v>
+      </c>
+      <c r="F11" s="169">
         <v>2</v>
       </c>
-      <c r="E8" s="172" t="s">
-        <v>267</v>
-      </c>
-      <c r="F8" s="172">
-        <v>4</v>
-      </c>
-      <c r="G8" s="173">
-        <v>32000</v>
-      </c>
-    </row>
-    <row r="9" spans="2:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D9" s="172">
-        <v>3</v>
-      </c>
-      <c r="E9" s="172" t="s">
-        <v>268</v>
-      </c>
-      <c r="F9" s="172">
-        <v>6</v>
-      </c>
-      <c r="G9" s="173">
-        <v>27000</v>
-      </c>
-    </row>
-    <row r="10" spans="2:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D10" s="172">
-        <v>4</v>
-      </c>
-      <c r="E10" s="172" t="s">
-        <v>269</v>
-      </c>
-      <c r="F10" s="172">
-        <v>5</v>
-      </c>
-      <c r="G10" s="173">
-        <v>19000</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D11" s="172">
-        <v>5</v>
-      </c>
-      <c r="E11" s="172" t="s">
-        <v>270</v>
-      </c>
-      <c r="F11" s="172">
-        <v>2</v>
-      </c>
-      <c r="G11" s="173">
+      <c r="G11" s="170">
         <v>12000</v>
       </c>
     </row>
     <row r="15" spans="2:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C15" s="2"/>
       <c r="D15" s="16" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E15" s="17"/>
       <c r="F15" s="17"/>
@@ -4861,51 +4888,51 @@
     </row>
     <row r="17" spans="4:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D17" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="F17" s="6" t="s">
         <v>273</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="18" spans="4:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D18" s="162" t="s">
-        <v>268</v>
-      </c>
-      <c r="E18" s="190" t="s">
-        <v>275</v>
-      </c>
-      <c r="F18" s="190">
+        <v>267</v>
+      </c>
+      <c r="E18" s="187" t="s">
+        <v>274</v>
+      </c>
+      <c r="F18" s="187">
         <v>1800</v>
       </c>
     </row>
     <row r="19" spans="4:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D19" s="162" t="s">
-        <v>267</v>
-      </c>
-      <c r="E19" s="190" t="s">
-        <v>276</v>
-      </c>
-      <c r="F19" s="190">
+        <v>266</v>
+      </c>
+      <c r="E19" s="187" t="s">
+        <v>275</v>
+      </c>
+      <c r="F19" s="187">
         <v>3200</v>
       </c>
     </row>
     <row r="20" spans="4:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D20" s="162" t="s">
-        <v>269</v>
-      </c>
-      <c r="E20" s="190" t="s">
-        <v>277</v>
-      </c>
-      <c r="F20" s="190">
+        <v>268</v>
+      </c>
+      <c r="E20" s="187" t="s">
+        <v>276</v>
+      </c>
+      <c r="F20" s="187">
         <v>1500</v>
       </c>
     </row>
     <row r="25" spans="4:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D25" s="16" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E25" s="17"/>
       <c r="F25" s="17"/>
@@ -4920,58 +4947,58 @@
     </row>
     <row r="27" spans="4:11" ht="13.5" x14ac:dyDescent="0.2">
       <c r="D27" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="E27" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="F27" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="F27" s="6" t="s">
+      <c r="G27" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="G27" s="6" t="s">
-        <v>265</v>
-      </c>
       <c r="H27" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="I27" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="I27" s="6" t="s">
+      <c r="J27" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="J27" s="6" t="s">
+      <c r="K27" s="6" t="s">
         <v>280</v>
-      </c>
-      <c r="K27" s="6" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="28" spans="4:11" ht="13.5" x14ac:dyDescent="0.2">
       <c r="D28" s="101">
         <v>2</v>
       </c>
-      <c r="E28" s="175" t="s">
-        <v>267</v>
-      </c>
-      <c r="F28" s="175" t="str">
+      <c r="E28" s="172" t="s">
+        <v>266</v>
+      </c>
+      <c r="F28" s="172" t="str">
         <f t="shared" ref="F28:F30" si="0">_xlfn.XLOOKUP($E28,$D$17:$D$20,E$17:E$20,"該当なし")</f>
         <v>鮑ステーキ</v>
       </c>
-      <c r="G28" s="174">
+      <c r="G28" s="171">
         <f>SUMIFS($F$8:$F$11,$E$8:$E$11,E28)</f>
         <v>4</v>
       </c>
-      <c r="H28" s="183">
+      <c r="H28" s="180">
         <f>_xlfn.XLOOKUP($E28,$D$17:$D$20,F$17:F$20,"該当なし")</f>
         <v>3200</v>
       </c>
-      <c r="I28" s="186">
+      <c r="I28" s="183">
         <f t="shared" ref="I28:I30" si="1">IFERROR(G28*H28,"-")</f>
         <v>12800</v>
       </c>
-      <c r="J28" s="186">
+      <c r="J28" s="183">
         <f>SUMIFS($G$8:$G$11,$E$8:$E$11,E28)</f>
         <v>32000</v>
       </c>
-      <c r="K28" s="176">
+      <c r="K28" s="173">
         <f t="shared" ref="K28:K30" si="2">IFERROR(I28/J28,"-")</f>
         <v>0.4</v>
       </c>
@@ -4980,30 +5007,30 @@
       <c r="D29" s="104">
         <v>3</v>
       </c>
-      <c r="E29" s="178" t="s">
-        <v>268</v>
-      </c>
-      <c r="F29" s="178" t="str">
+      <c r="E29" s="175" t="s">
+        <v>267</v>
+      </c>
+      <c r="F29" s="175" t="str">
         <f t="shared" si="0"/>
         <v>金目鯛煮付</v>
       </c>
-      <c r="G29" s="177">
+      <c r="G29" s="174">
         <f t="shared" ref="G29:G31" si="3">SUMIFS($F$8:$F$11,$E$8:$E$11,E29)</f>
         <v>6</v>
       </c>
-      <c r="H29" s="184">
+      <c r="H29" s="181">
         <f t="shared" ref="H29:H31" si="4">_xlfn.XLOOKUP($E29,$D$17:$D$20,F$17:F$20,"該当なし")</f>
         <v>1800</v>
       </c>
-      <c r="I29" s="187">
+      <c r="I29" s="184">
         <f t="shared" si="1"/>
         <v>10800</v>
       </c>
-      <c r="J29" s="187">
+      <c r="J29" s="184">
         <f t="shared" ref="J29:J31" si="5">SUMIFS($G$8:$G$11,$E$8:$E$11,E29)</f>
         <v>27000</v>
       </c>
-      <c r="K29" s="179">
+      <c r="K29" s="176">
         <f t="shared" si="2"/>
         <v>0.4</v>
       </c>
@@ -5012,62 +5039,62 @@
       <c r="D30" s="104">
         <v>4</v>
       </c>
-      <c r="E30" s="178" t="s">
-        <v>269</v>
-      </c>
-      <c r="F30" s="178" t="str">
+      <c r="E30" s="175" t="s">
+        <v>268</v>
+      </c>
+      <c r="F30" s="175" t="str">
         <f t="shared" si="0"/>
         <v>地魚刺身盛</v>
       </c>
-      <c r="G30" s="177">
+      <c r="G30" s="174">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="H30" s="184">
+      <c r="H30" s="181">
         <f t="shared" si="4"/>
         <v>1500</v>
       </c>
-      <c r="I30" s="187">
+      <c r="I30" s="184">
         <f t="shared" si="1"/>
         <v>7500</v>
       </c>
-      <c r="J30" s="187">
+      <c r="J30" s="184">
         <f t="shared" si="5"/>
         <v>19000</v>
       </c>
-      <c r="K30" s="179">
+      <c r="K30" s="176">
         <f t="shared" si="2"/>
         <v>0.39473684210526316</v>
       </c>
     </row>
     <row r="31" spans="4:11" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="D31" s="170">
+      <c r="D31" s="167">
         <v>5</v>
       </c>
-      <c r="E31" s="181" t="s">
-        <v>270</v>
-      </c>
-      <c r="F31" s="181" t="str">
+      <c r="E31" s="178" t="s">
+        <v>269</v>
+      </c>
+      <c r="F31" s="178" t="str">
         <f>_xlfn.XLOOKUP($E31,$D$17:$D$20,E$17:E$20,"該当なし")</f>
         <v>該当なし</v>
       </c>
-      <c r="G31" s="180">
+      <c r="G31" s="177">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="H31" s="185" t="str">
+      <c r="H31" s="182" t="str">
         <f t="shared" si="4"/>
         <v>該当なし</v>
       </c>
-      <c r="I31" s="188" t="str">
+      <c r="I31" s="185" t="str">
         <f>IFERROR(G31*H31,"-")</f>
         <v>-</v>
       </c>
-      <c r="J31" s="188">
+      <c r="J31" s="185">
         <f t="shared" si="5"/>
         <v>12000</v>
       </c>
-      <c r="K31" s="182" t="str">
+      <c r="K31" s="179" t="str">
         <f>IFERROR(I31/J31,"-")</f>
         <v>-</v>
       </c>
@@ -5080,287 +5107,327 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="B2:I31"/>
+  <dimension ref="B2:J31"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="2.36328125" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
     <col min="5" max="5" width="22" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="8" max="8" width="24" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="6" max="7" width="14" customWidth="1"/>
+    <col min="9" max="9" width="24" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="64" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="2:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D4" s="3" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D5" s="66" t="s">
         <v>90</v>
       </c>
       <c r="E5" s="67"/>
       <c r="F5" s="67"/>
-      <c r="H5" s="97" t="s">
+      <c r="G5" s="67"/>
+      <c r="I5" s="97" t="s">
         <v>240</v>
       </c>
-      <c r="I5" s="67"/>
-    </row>
-    <row r="6" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="7" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J5" s="67"/>
+    </row>
+    <row r="6" spans="2:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="2:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D7" s="68" t="s">
         <v>66</v>
       </c>
       <c r="E7" s="68" t="s">
         <v>91</v>
       </c>
-      <c r="F7" s="68" t="s">
+      <c r="F7" s="138" t="s">
+        <v>282</v>
+      </c>
+      <c r="G7" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="H7" s="68" t="s">
+      <c r="I7" s="68" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="8" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D8" s="69" t="s">
         <v>70</v>
       </c>
       <c r="E8" s="69" t="s">
         <v>93</v>
       </c>
-      <c r="F8" s="70">
+      <c r="F8" s="102" t="s">
+        <v>283</v>
+      </c>
+      <c r="G8" s="70">
         <v>160000</v>
       </c>
-      <c r="H8" s="98" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I8" s="98" t="s">
+        <v>285</v>
+      </c>
+      <c r="J8" s="98"/>
+    </row>
+    <row r="9" spans="2:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D9" s="72" t="s">
         <v>71</v>
       </c>
       <c r="E9" s="72" t="s">
         <v>94</v>
       </c>
-      <c r="F9" s="73">
+      <c r="F9" s="72" t="s">
+        <v>283</v>
+      </c>
+      <c r="G9" s="73">
         <v>108000</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I9" s="3" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D10" s="72" t="s">
         <v>73</v>
       </c>
       <c r="E10" s="72" t="s">
         <v>95</v>
       </c>
-      <c r="F10" s="73">
+      <c r="F10" s="99" t="s">
+        <v>284</v>
+      </c>
+      <c r="G10" s="73">
         <v>72000</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I10" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D11" s="72" t="s">
         <v>74</v>
       </c>
       <c r="E11" s="72" t="s">
         <v>93</v>
       </c>
-      <c r="F11" s="73">
+      <c r="F11" s="72" t="s">
+        <v>283</v>
+      </c>
+      <c r="G11" s="73">
         <v>180000</v>
       </c>
-    </row>
-    <row r="12" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I11" s="188"/>
+    </row>
+    <row r="12" spans="2:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D12" s="72" t="s">
         <v>75</v>
       </c>
       <c r="E12" s="72" t="s">
         <v>96</v>
       </c>
-      <c r="F12" s="73">
+      <c r="F12" s="72" t="s">
+        <v>283</v>
+      </c>
+      <c r="G12" s="73">
         <v>95000</v>
       </c>
     </row>
-    <row r="13" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D13" s="72" t="s">
         <v>76</v>
       </c>
       <c r="E13" s="72" t="s">
         <v>94</v>
       </c>
-      <c r="F13" s="73">
+      <c r="F13" s="72" t="s">
+        <v>283</v>
+      </c>
+      <c r="G13" s="73">
         <v>36000</v>
       </c>
     </row>
-    <row r="14" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D14" s="72" t="s">
         <v>77</v>
       </c>
       <c r="E14" s="72" t="s">
         <v>97</v>
       </c>
-      <c r="F14" s="73">
+      <c r="F14" s="99" t="s">
+        <v>284</v>
+      </c>
+      <c r="G14" s="73">
         <v>152000</v>
       </c>
-      <c r="H14" s="97" t="s">
+      <c r="I14" s="97" t="s">
         <v>241</v>
       </c>
-      <c r="I14" s="67"/>
-    </row>
-    <row r="15" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J14" s="67"/>
+    </row>
+    <row r="15" spans="2:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D15" s="72" t="s">
         <v>78</v>
       </c>
       <c r="E15" s="72" t="s">
         <v>95</v>
       </c>
-      <c r="F15" s="73">
+      <c r="F15" s="99" t="s">
+        <v>284</v>
+      </c>
+      <c r="G15" s="73">
         <v>74000</v>
       </c>
     </row>
-    <row r="16" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D16" s="72" t="s">
         <v>79</v>
       </c>
       <c r="E16" s="72" t="s">
         <v>93</v>
       </c>
-      <c r="F16" s="73">
+      <c r="F16" s="72" t="s">
+        <v>283</v>
+      </c>
+      <c r="G16" s="73">
         <v>92000</v>
       </c>
-      <c r="H16" s="68" t="s">
+      <c r="I16" s="68" t="s">
         <v>101</v>
       </c>
-      <c r="I16" s="68" t="s">
+      <c r="J16" s="68" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="17" spans="4:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="4:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D17" s="72" t="s">
         <v>80</v>
       </c>
       <c r="E17" s="72" t="s">
         <v>96</v>
       </c>
-      <c r="F17" s="73">
+      <c r="F17" s="72" t="s">
+        <v>283</v>
+      </c>
+      <c r="G17" s="73">
         <v>270000</v>
       </c>
-      <c r="H17" s="69" t="str" cm="1">
-        <f t="array" ref="H17:H22">_xlfn._xlws.SORT(_xlfn.UNIQUE(E8:E19))</f>
-        <v>Booking.com</v>
-      </c>
-      <c r="I17" s="70" cm="1">
-        <f t="array" ref="I17:I22">SUMIFS($F$8:$F$19,$E$8:$E$19,_xlfn.ANCHORARRAY(H17))</f>
-        <v>146000</v>
-      </c>
-    </row>
-    <row r="18" spans="4:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I17" s="69" t="str" cm="1">
+        <f t="array" ref="I17:I20">_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(E8:E19, F8:F19="国内")))</f>
+        <v>じゃらん</v>
+      </c>
+      <c r="J17" s="70" cm="1">
+        <f t="array" ref="J17:J20">SUMIFS($G$8:$G$19,$E$8:$E$19,_xlfn.ANCHORARRAY(I17))</f>
+        <v>208000</v>
+      </c>
+    </row>
+    <row r="18" spans="4:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D18" s="72" t="s">
         <v>99</v>
       </c>
       <c r="E18" s="72" t="s">
         <v>98</v>
       </c>
-      <c r="F18" s="73">
+      <c r="F18" s="72" t="s">
+        <v>283</v>
+      </c>
+      <c r="G18" s="73">
         <v>210000</v>
       </c>
-      <c r="H18" s="72" t="str">
-        <v>Expedia</v>
-      </c>
-      <c r="I18" s="73">
-        <v>152000</v>
-      </c>
-    </row>
-    <row r="19" spans="4:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I18" s="72" t="str">
+        <v>一休.com</v>
+      </c>
+      <c r="J18" s="73">
+        <v>210000</v>
+      </c>
+    </row>
+    <row r="19" spans="4:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D19" s="72" t="s">
         <v>100</v>
       </c>
       <c r="E19" s="72" t="s">
         <v>94</v>
       </c>
-      <c r="F19" s="73">
+      <c r="F19" s="72" t="s">
+        <v>283</v>
+      </c>
+      <c r="G19" s="73">
         <v>64000</v>
       </c>
-      <c r="H19" s="72" t="str">
-        <v>じゃらん</v>
-      </c>
-      <c r="I19" s="73">
-        <v>208000</v>
-      </c>
-    </row>
-    <row r="20" spans="4:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I19" s="72" t="str">
+        <v>楽天トラベル</v>
+      </c>
+      <c r="J19" s="73">
+        <v>432000</v>
+      </c>
+    </row>
+    <row r="20" spans="4:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D20" s="72"/>
       <c r="E20" s="99" t="s">
-        <v>245</v>
-      </c>
-      <c r="F20" s="73"/>
-      <c r="H20" s="72" t="str">
-        <v>一休.com</v>
-      </c>
-      <c r="I20" s="73">
-        <v>210000</v>
-      </c>
-    </row>
-    <row r="21" spans="4:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>244</v>
+      </c>
+      <c r="F20" s="99"/>
+      <c r="G20" s="73"/>
+      <c r="I20" s="72" t="str">
+        <v>公式サイト</v>
+      </c>
+      <c r="J20" s="73">
+        <v>365000</v>
+      </c>
+    </row>
+    <row r="21" spans="4:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D21" s="72"/>
       <c r="E21" s="72"/>
-      <c r="F21" s="73"/>
-      <c r="H21" s="72" t="str">
-        <v>楽天トラベル</v>
-      </c>
-      <c r="I21" s="73">
-        <v>432000</v>
-      </c>
-    </row>
-    <row r="22" spans="4:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F21" s="72"/>
+      <c r="G21" s="73"/>
+      <c r="I21" s="72"/>
+      <c r="J21" s="73"/>
+    </row>
+    <row r="22" spans="4:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D22" s="72"/>
       <c r="E22" s="72"/>
-      <c r="F22" s="73"/>
-      <c r="H22" s="72" t="str">
-        <v>公式サイト</v>
-      </c>
-      <c r="I22" s="73">
-        <v>365000</v>
-      </c>
-    </row>
-    <row r="23" spans="4:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F22" s="72"/>
+      <c r="G22" s="73"/>
+      <c r="I22" s="72"/>
+      <c r="J22" s="73"/>
+    </row>
+    <row r="23" spans="4:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D23" s="72"/>
       <c r="E23" s="72"/>
-      <c r="F23" s="73"/>
-      <c r="H23" s="72"/>
-      <c r="I23" s="73"/>
-    </row>
-    <row r="24" spans="4:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F23" s="72"/>
+      <c r="G23" s="73"/>
+      <c r="I23" s="72"/>
+      <c r="J23" s="73"/>
+    </row>
+    <row r="24" spans="4:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D24" s="72"/>
       <c r="E24" s="72"/>
-      <c r="F24" s="73"/>
-      <c r="H24" s="72"/>
-      <c r="I24" s="73"/>
-    </row>
-    <row r="25" spans="4:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F24" s="72"/>
+      <c r="G24" s="73"/>
+      <c r="I24" s="72"/>
+      <c r="J24" s="73"/>
+    </row>
+    <row r="25" spans="4:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D25" s="72"/>
       <c r="E25" s="72"/>
-      <c r="F25" s="73"/>
-      <c r="H25" s="72"/>
-      <c r="I25" s="73"/>
-    </row>
-    <row r="26" spans="4:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="4:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="4:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="4:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="4:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="4:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="F25" s="72"/>
+      <c r="G25" s="73"/>
+      <c r="I25" s="72"/>
+      <c r="J25" s="73"/>
+    </row>
+    <row r="26" spans="4:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="4:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="4:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="4:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="4:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="4:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <phoneticPr fontId="11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5477,7 +5544,7 @@
     <row r="16" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="17" spans="4:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D17" s="97" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E17" s="67"/>
       <c r="F17" s="67"/>
@@ -5557,7 +5624,7 @@
     <row r="3" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D4" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5588,7 +5655,7 @@
         <v>20</v>
       </c>
       <c r="F8" s="101" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="9" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5600,7 +5667,7 @@
         <v>365</v>
       </c>
       <c r="F9" s="104" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5612,12 +5679,12 @@
         <v>0.65</v>
       </c>
       <c r="F10" s="106" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D11" s="112" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E11" s="119">
         <f>E8*E9*E10</f>
@@ -5638,7 +5705,7 @@
         <v>50000</v>
       </c>
       <c r="F13" s="71" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="14" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5660,14 +5727,14 @@
     </row>
     <row r="16" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D16" s="102" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E16" s="122">
         <f>'2-4_PL①Input'!E12</f>
         <v>2</v>
       </c>
       <c r="F16" s="69" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="17" spans="4:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5680,7 +5747,7 @@
         <v>6000</v>
       </c>
       <c r="F17" s="74" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="18" spans="4:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5692,7 +5759,7 @@
         <v>56940000</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="19" spans="4:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5719,14 +5786,14 @@
     </row>
     <row r="22" spans="4:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D22" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E22" s="103">
         <f>'2-4_PL①Input'!E20</f>
         <v>0.3</v>
       </c>
       <c r="F22" s="109" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="23" spans="4:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5842,7 +5909,7 @@
     <row r="3" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D4" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="5" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5854,7 +5921,7 @@
     </row>
     <row r="6" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D6" s="145" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -5863,10 +5930,10 @@
         <v>105</v>
       </c>
       <c r="E8" s="138" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F8" s="138" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="9" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5885,7 +5952,7 @@
     <row r="10" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="11" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D11" s="114" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E11" s="121">
         <f>'2-4_PL②計算'!E23/10^6</f>
@@ -5912,7 +5979,7 @@
     <row r="13" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="14" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D14" s="114" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E14" s="121">
         <f>'2-4_PL②計算'!E28/10^6</f>

--- a/files/excel-mastery-full.xlsx
+++ b/files/excel-mastery-full.xlsx
@@ -33,7 +33,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
@@ -41,8 +41,9 @@
     <numFmt numFmtId="168" formatCode="#,##0.00000"/>
     <numFmt numFmtId="169" formatCode="#,##0.0%;[Red]\-#,##0.0%"/>
     <numFmt numFmtId="170" formatCode="0.000"/>
+    <numFmt numFmtId="171" formatCode="yyyy/m/d"/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="41">
     <font>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
@@ -280,6 +281,51 @@
       <color rgb="FF000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="128"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color rgb="FF002060"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="128"/>
+      <family val="3"/>
+      <color rgb="FFFF0000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="128"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="128"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="128"/>
+      <family val="3"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -337,7 +383,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -659,6 +705,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
@@ -672,7 +733,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="240">
+  <cellXfs count="258">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -1361,6 +1422,34 @@
     <xf numFmtId="165" fontId="22" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="8" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="38" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="9" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="10" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="10" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="8" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="10" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="40" fillId="10" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="40" fillId="9" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1803,7 +1892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="B2:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
     <col width="2.36328125" customWidth="1" min="1" max="3"/>
@@ -1811,7 +1900,6 @@
     <col width="12.26953125" customWidth="1" min="5" max="9"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="19.5" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -1820,8 +1908,6 @@
       </c>
       <c r="C2" s="1" t="n"/>
     </row>
-    <row r="3"/>
-    <row r="4"/>
     <row r="5" ht="13.5" customHeight="1">
       <c r="C5" s="2" t="n"/>
       <c r="D5" s="16" t="inlineStr">
@@ -1999,9 +2085,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
     <row r="20" ht="13.5" customHeight="1">
       <c r="C20" s="2" t="n"/>
       <c r="D20" s="16" t="inlineStr">
@@ -2189,7 +2272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="B2:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
     <col width="2.36328125" customWidth="1" min="1" max="3"/>
@@ -2198,7 +2281,6 @@
     <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="19.5" customHeight="1">
       <c r="B2" s="64" t="inlineStr">
         <is>
@@ -2346,7 +2428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="B2:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
     <col width="2.36328125" customWidth="1" min="1" max="3"/>
@@ -2355,7 +2437,6 @@
     <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="19.5" customHeight="1">
       <c r="B2" s="64" t="inlineStr">
         <is>
@@ -2611,7 +2692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="B2:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
     <col width="2.36328125" customWidth="1" min="1" max="3"/>
@@ -2620,7 +2701,6 @@
     <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="19.5" customHeight="1">
       <c r="B2" s="64" t="inlineStr">
         <is>
@@ -2722,7 +2802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="B2:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
     <col width="2.36328125" customWidth="1" min="1" max="3"/>
@@ -2733,7 +2813,6 @@
     <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="19.5" customHeight="1">
       <c r="B2" s="64" t="inlineStr">
         <is>
@@ -3069,7 +3148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="B2:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
     <col width="2.36328125" customWidth="1" min="1" max="3"/>
@@ -3077,7 +3156,6 @@
     <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="19.5" customHeight="1">
       <c r="B2" s="64" t="inlineStr">
         <is>
@@ -3177,7 +3255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="B2:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
     <col width="2.36328125" customWidth="1" min="1" max="3"/>
@@ -3187,7 +3265,6 @@
     <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="19.5" customHeight="1">
       <c r="B2" s="64" t="inlineStr">
         <is>
@@ -3316,14 +3393,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="B2:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
     <col width="2.36328125" customWidth="1" min="1" max="3"/>
     <col width="16" customWidth="1" min="4" max="5"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="19.5" customHeight="1">
       <c r="B2" s="64" t="inlineStr">
         <is>
@@ -3405,7 +3481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="B2:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
     <col width="2.36328125" customWidth="1" min="1" max="3"/>
@@ -3414,7 +3490,6 @@
     <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="19.5" customHeight="1">
       <c r="B2" s="64" t="inlineStr">
         <is>
@@ -3554,7 +3629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="B2:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
     <col width="2.36328125" customWidth="1" min="1" max="3"/>
@@ -3564,7 +3639,6 @@
     <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="19.5" customHeight="1">
       <c r="B2" s="64" t="inlineStr">
         <is>
@@ -3748,7 +3822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="B2:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
     <col width="2.36328125" customWidth="1" min="1" max="3"/>
@@ -3759,7 +3833,6 @@
     <col width="30" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="19.5" customHeight="1">
       <c r="B2" s="64" t="inlineStr">
         <is>
@@ -3914,7 +3987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="B2:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
     <col width="2.36328125" customWidth="1" min="1" max="3"/>
@@ -3924,7 +3997,6 @@
     <col width="28" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="19.5" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -3933,8 +4005,6 @@
       </c>
       <c r="C2" s="1" t="n"/>
     </row>
-    <row r="3"/>
-    <row r="4"/>
     <row r="5" ht="13.5" customHeight="1">
       <c r="D5" s="16" t="inlineStr">
         <is>
@@ -3947,7 +4017,6 @@
       <c r="H5" s="16" t="n"/>
       <c r="I5" s="16" t="n"/>
     </row>
-    <row r="6"/>
     <row r="7" ht="13.5" customHeight="1">
       <c r="D7" s="6" t="inlineStr">
         <is>
@@ -4048,7 +4117,6 @@
       <c r="H11" s="12" t="n"/>
       <c r="I11" s="12" t="n"/>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="D13" s="3" t="inlineStr">
         <is>
@@ -4123,9 +4191,6 @@
         <v/>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
     <row r="23" ht="13.5" customHeight="1">
       <c r="C23" s="2" t="n"/>
       <c r="D23" s="16" t="inlineStr">
@@ -4139,7 +4204,6 @@
       <c r="H23" s="16" t="n"/>
       <c r="I23" s="16" t="n"/>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="D25" s="3" t="inlineStr">
         <is>
@@ -4240,8 +4304,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34"/>
     <row r="35" ht="13.5" customHeight="1">
       <c r="D35" s="16" t="inlineStr">
         <is>
@@ -4389,7 +4451,6 @@
         <v/>
       </c>
     </row>
-    <row r="44"/>
     <row r="45">
       <c r="D45" s="3" t="inlineStr">
         <is>
@@ -4423,7 +4484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J47"/>
+  <dimension ref="B2:J47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
     <col width="2.36328125" customWidth="1" min="1" max="3"/>
@@ -4431,7 +4492,6 @@
     <col width="12.26953125" customWidth="1" min="5" max="10"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="19.5" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -4793,9 +4853,6 @@
         <v>270000</v>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
     <row r="21" ht="13.5" customHeight="1">
       <c r="C21" s="2" t="n"/>
       <c r="D21" s="16" t="inlineStr">
@@ -4896,10 +4953,6 @@
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
     <row r="32" ht="13.5" customHeight="1">
       <c r="D32" s="16" t="inlineStr">
         <is>
@@ -4989,14 +5042,6 @@
         </is>
       </c>
     </row>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
     <row r="47" ht="13.5" customHeight="1">
       <c r="D47" s="56" t="n"/>
       <c r="E47" s="63" t="n"/>
@@ -5014,7 +5059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="B2:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
     <col width="2.36328125" customWidth="1" min="1" max="3"/>
@@ -5023,7 +5068,6 @@
     <col width="9.453125" bestFit="1" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="19.5" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -5145,9 +5189,6 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
     <row r="15" ht="13.5" customHeight="1">
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="16" t="inlineStr">
@@ -5229,10 +5270,6 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
     <row r="25" ht="13.5" customHeight="1">
       <c r="D25" s="16" t="inlineStr">
         <is>
@@ -5439,7 +5476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="B2:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
     <col width="2.36328125" customWidth="1" min="1" max="3"/>
@@ -5450,7 +5487,6 @@
     <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="19.5" customHeight="1">
       <c r="B2" s="64" t="inlineStr">
         <is>
@@ -5882,646 +5918,741 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:K130"/>
+  <dimension ref="A1:M114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="2.4" customWidth="1" min="1" max="1"/>
+    <col width="2.36328125" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="3" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="3" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="B2" s="197" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="16.5" customHeight="1">
+      <c r="B2" s="240" t="inlineStr">
         <is>
           <t>2-2-2. データ加工・クリーニング ― スピル関数系（UNIQUE / FILTER / SORTBY / TOCOL / TOROW / DROP / TEXTSPLIT / SEQUENCE）</t>
         </is>
       </c>
+      <c r="C2" s="240" t="n"/>
     </row>
     <row r="3">
-      <c r="B3" s="198" t="inlineStr">
-        <is>
-          <t>各「数式」セル（青）はExcelで開くと自動計算し、下・右方向にスピルします。※動的配列に対応した Microsoft 365 が必要です。</t>
-        </is>
-      </c>
-    </row>
+      <c r="B3" s="241" t="inlineStr">
+        <is>
+          <t>各「数式」セル（青）はExcelで開くと自動計算し、下方向・右方向にスピル（spill）します。※動的配列に対応した Microsoft 365 が必要です。</t>
+        </is>
+      </c>
+      <c r="C3" s="241" t="n"/>
+    </row>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6">
-      <c r="B6" s="199" t="inlineStr">
+      <c r="B6" s="242" t="inlineStr">
         <is>
           <t>【元データ】予約明細（空白セルと『合計』行をわざと含む）</t>
         </is>
       </c>
+      <c r="H6" s="242" t="inlineStr">
+        <is>
+          <t>① UNIQUE + TOCOL ｜ 空白を集計しない</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="B7" s="200" t="inlineStr">
+      <c r="B7" s="243" t="inlineStr">
         <is>
           <t>予約ID</t>
         </is>
       </c>
-      <c r="C7" s="200" t="inlineStr">
+      <c r="C7" s="243" t="inlineStr">
+        <is>
+          <t>予約経路ID</t>
+        </is>
+      </c>
+      <c r="D7" s="243" t="inlineStr">
         <is>
           <t>予約経路</t>
         </is>
       </c>
-      <c r="D7" s="200" t="inlineStr">
+      <c r="E7" s="243" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="E7" s="200" t="inlineStr">
+      <c r="F7" s="243" t="inlineStr">
         <is>
           <t>売上</t>
         </is>
       </c>
+      <c r="H7" s="241" t="inlineStr">
+        <is>
+          <t>UNIQUE で重複除去。</t>
+        </is>
+      </c>
+      <c r="J7" s="241" t="inlineStr">
+        <is>
+          <t>TOCOL(範囲,1) で1列に畳みつつ空白を無視 → UNIQUE で重複除去。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="B8" s="201" t="inlineStr">
+      <c r="B8" s="244" t="inlineStr">
         <is>
           <t>R001</t>
         </is>
       </c>
-      <c r="C8" s="202" t="inlineStr">
+      <c r="C8" s="244" t="inlineStr">
+        <is>
+          <t>RC001</t>
+        </is>
+      </c>
+      <c r="D8" s="245" t="inlineStr">
         <is>
           <t>楽天トラベル</t>
         </is>
       </c>
-      <c r="D8" s="201" t="inlineStr">
+      <c r="E8" s="244" t="inlineStr">
         <is>
           <t>国内</t>
         </is>
       </c>
-      <c r="E8" s="203" t="n">
+      <c r="F8" s="246" t="n">
         <v>160000</v>
       </c>
+      <c r="H8" s="247">
+        <f t="array" ref="H8:H14">_xlfn.UNIQUE(D:D)</f>
+        <v/>
+      </c>
+      <c r="J8" s="247">
+        <f t="array" ref="J8:J13">_xlfn.UNIQUE(_xlfn.TOCOL(D:D,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
-      <c r="B9" s="201" t="inlineStr">
+      <c r="B9" s="244" t="inlineStr">
         <is>
           <t>R002</t>
         </is>
       </c>
-      <c r="C9" s="202" t="inlineStr">
+      <c r="C9" s="244" t="inlineStr">
+        <is>
+          <t>RC002</t>
+        </is>
+      </c>
+      <c r="D9" s="245" t="inlineStr">
         <is>
           <t>じゃらん</t>
         </is>
       </c>
-      <c r="D9" s="201" t="inlineStr">
+      <c r="E9" s="244" t="inlineStr">
         <is>
           <t>国内</t>
         </is>
       </c>
-      <c r="E9" s="203" t="n">
+      <c r="F9" s="246" t="n">
         <v>108000</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="201" t="inlineStr">
+      <c r="B10" s="244" t="inlineStr">
         <is>
           <t>R003</t>
         </is>
       </c>
-      <c r="C10" s="202" t="inlineStr">
+      <c r="C10" s="244" t="inlineStr">
+        <is>
+          <t>RC005</t>
+        </is>
+      </c>
+      <c r="D10" s="245" t="inlineStr">
         <is>
           <t>Booking.com</t>
         </is>
       </c>
-      <c r="D10" s="201" t="inlineStr">
+      <c r="E10" s="244" t="inlineStr">
         <is>
           <t>海外</t>
         </is>
       </c>
-      <c r="E10" s="203" t="n">
+      <c r="F10" s="246" t="n">
         <v>72000</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="201" t="inlineStr">
+      <c r="B11" s="244" t="inlineStr">
         <is>
           <t>R004</t>
         </is>
       </c>
-      <c r="C11" s="202" t="n"/>
-      <c r="D11" s="201" t="inlineStr">
+      <c r="C11" s="244" t="n"/>
+      <c r="D11" s="245" t="n"/>
+      <c r="E11" s="244" t="inlineStr">
         <is>
           <t>国内</t>
         </is>
       </c>
-      <c r="E11" s="203" t="n">
+      <c r="F11" s="246" t="n">
         <v>180000</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="201" t="inlineStr">
+      <c r="B12" s="244" t="inlineStr">
         <is>
           <t>R005</t>
         </is>
       </c>
-      <c r="C12" s="202" t="inlineStr">
+      <c r="C12" s="244" t="inlineStr">
+        <is>
+          <t>RC010</t>
+        </is>
+      </c>
+      <c r="D12" s="245" t="inlineStr">
         <is>
           <t>公式サイト</t>
         </is>
       </c>
-      <c r="D12" s="201" t="inlineStr">
+      <c r="E12" s="244" t="inlineStr">
         <is>
           <t>国内</t>
         </is>
       </c>
-      <c r="E12" s="203" t="n">
+      <c r="F12" s="246" t="n">
         <v>95000</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="201" t="inlineStr">
+      <c r="B13" s="244" t="inlineStr">
         <is>
           <t>R006</t>
         </is>
       </c>
-      <c r="C13" s="202" t="inlineStr">
+      <c r="C13" s="244" t="inlineStr">
+        <is>
+          <t>RC002</t>
+        </is>
+      </c>
+      <c r="D13" s="245" t="inlineStr">
         <is>
           <t>じゃらん</t>
         </is>
       </c>
-      <c r="D13" s="201" t="inlineStr">
+      <c r="E13" s="244" t="inlineStr">
         <is>
           <t>国内</t>
         </is>
       </c>
-      <c r="E13" s="203" t="n">
+      <c r="F13" s="246" t="n">
         <v>36000</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="201" t="inlineStr">
+      <c r="B14" s="244" t="inlineStr">
         <is>
           <t>R007</t>
         </is>
       </c>
-      <c r="C14" s="202" t="inlineStr">
+      <c r="C14" s="244" t="inlineStr">
+        <is>
+          <t>RC008</t>
+        </is>
+      </c>
+      <c r="D14" s="245" t="inlineStr">
         <is>
           <t>Expedia</t>
         </is>
       </c>
-      <c r="D14" s="201" t="inlineStr">
+      <c r="E14" s="244" t="inlineStr">
         <is>
           <t>海外</t>
         </is>
       </c>
-      <c r="E14" s="203" t="n">
+      <c r="F14" s="246" t="n">
         <v>152000</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="201" t="inlineStr">
+      <c r="B15" s="244" t="inlineStr">
         <is>
           <t>R008</t>
         </is>
       </c>
-      <c r="C15" s="202" t="n"/>
-      <c r="D15" s="201" t="inlineStr">
+      <c r="C15" s="244" t="n"/>
+      <c r="D15" s="245" t="n"/>
+      <c r="E15" s="244" t="inlineStr">
         <is>
           <t>海外</t>
         </is>
       </c>
-      <c r="E15" s="203" t="n">
+      <c r="F15" s="246" t="n">
         <v>74000</v>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="201" t="inlineStr">
+      <c r="B16" s="244" t="inlineStr">
         <is>
           <t>R009</t>
         </is>
       </c>
-      <c r="C16" s="202" t="inlineStr">
+      <c r="C16" s="244" t="inlineStr">
+        <is>
+          <t>RC001</t>
+        </is>
+      </c>
+      <c r="D16" s="245" t="inlineStr">
         <is>
           <t>楽天トラベル</t>
         </is>
       </c>
-      <c r="D16" s="201" t="inlineStr">
+      <c r="E16" s="244" t="inlineStr">
         <is>
           <t>国内</t>
         </is>
       </c>
-      <c r="E16" s="203" t="n">
+      <c r="F16" s="246" t="n">
         <v>92000</v>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="201" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C17" s="202" t="inlineStr">
-        <is>
-          <t>合計</t>
-        </is>
-      </c>
-      <c r="D17" s="201" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E17" s="203" t="n">
-        <v>969000</v>
+    <row r="17"/>
+    <row r="18">
+      <c r="B18" s="241" t="inlineStr">
+        <is>
+          <t>※ C7がヘッダー、C11・C15 が空白</t>
+        </is>
+      </c>
+      <c r="C18" s="241" t="n"/>
+      <c r="H18" s="242" t="inlineStr">
+        <is>
+          <t>② UNIQUE + TOCOL + FILTER ｜ 空白＋特定セル(合計)を除外＝実データのみ</t>
+        </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="198" t="inlineStr">
-        <is>
-          <t>※ C11・C15 が空白、C17 が『合計』。これらを除いて“実データのみ”を取り出すのが下の例です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="199" t="inlineStr">
-        <is>
-          <t>① UNIQUE + TOCOL ｜ 空白を集計しない</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="198" t="inlineStr">
-        <is>
-          <t>TOCOL(範囲,1) で1列に畳みつつ空白を無視 → UNIQUE で重複除去。</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="204">
-        <f>UNIQUE(TOCOL(C8:C17,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="199" t="inlineStr">
-        <is>
-          <t>② UNIQUE + TOCOL + FILTER ｜ 空白＋特定セル(合計)を除外＝実データのみ</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="198" t="inlineStr">
-        <is>
-          <t>FILTER で『合計』を除外 → TOCOL(,1) で空白無視 → UNIQUE。</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="204">
-        <f>UNIQUE(TOCOL(FILTER(C8:C17,C8:C17&lt;&gt;"合計"),1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" s="199" t="inlineStr">
+      <c r="B19" s="241" t="inlineStr">
+        <is>
+          <t>これらを除いて“実データのみ”を取り出すのが右の例です。</t>
+        </is>
+      </c>
+      <c r="C19" s="241" t="n"/>
+      <c r="H19" s="241" t="inlineStr">
+        <is>
+          <t>FILTER で『予約経路』を除外 → TOCOL(,1) で空白無視 → UNIQUE。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="H20" s="247">
+        <f t="array" ref="H20:H24">_xlfn.UNIQUE(_xlfn.TOCOL(_xlfn._xlws.FILTER(D:D,D:D&lt;&gt;"予約経路"),1))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30">
+      <c r="H30" s="242" t="inlineStr">
         <is>
           <t>③ UNIQUE + TOCOL + DROP ｜ 空白＋先頭の任意行を除外</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="B47" s="198" t="inlineStr">
-        <is>
-          <t>DROP(範囲,3) で先頭3行を落とす → TOCOL(,1) → UNIQUE。前置き行の除去に。</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="204">
-        <f>UNIQUE(TOCOL(DROP(C8:C17,3),1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="B58" s="199" t="inlineStr">
-        <is>
-          <t>④ ③ + SORTBY ｜ さらに任意の順で並べ替え（ここでは降順）</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="198" t="inlineStr">
+    <row r="31">
+      <c r="H31" s="241" t="inlineStr">
+        <is>
+          <t>DROP(範囲,7) で先頭7行を落とす → TOCOL(,1) → UNIQUE。ヘッダや前置き行を飛ばす用途。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="H32" s="247">
+        <f t="array" ref="H32:H36">_xlfn.UNIQUE(_xlfn.TOCOL(_xlfn.DROP(D:D,7),1))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42">
+      <c r="H42" s="242" t="inlineStr">
+        <is>
+          <t>④ ③ + SORT ｜ さらに任意の順で並べ替え（ここでは降順）</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="H43" s="241" t="inlineStr">
+        <is>
+          <t>SORT(結果, 並べ替えキーの列番号, -1)。キー配列を差し替えれば任意の順に。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="H44" s="247">
+        <f t="array" ref="H44:H48">_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn.TOCOL(_xlfn.DROP(D:D,7),1)),1,-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54">
+      <c r="H54" s="242" t="inlineStr">
+        <is>
+          <t>⑤ ③ + SORTBY ｜ さらに任意の順で並べ替え（ここでは昇順）</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="H55" s="241" t="inlineStr">
         <is>
           <t>SORTBY(結果, 並べ替えキー, -1)。キー配列を差し替えれば任意の順に。</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="B60" s="204">
-        <f>SORTBY(UNIQUE(TOCOL(DROP(C8:C17,3),1)),UNIQUE(TOCOL(DROP(C8:C17,3),1)),-1)</f>
-        <v/>
+    <row r="56">
+      <c r="H56" s="247">
+        <f t="array" ref="H56:H60">_xlfn.SORTBY(
+                _xlfn.UNIQUE(_xlfn.TOCOL(_xlfn.DROP(C:C,7),1)),
+                _xlfn.UNIQUE(_xlfn.TOCOL(_xlfn.DROP(C:C,7),1)),
+                1
+               )</f>
+        <v/>
+      </c>
+      <c r="I56" s="247">
+        <f t="array" ref="I56:I60">_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(H56),C:C,D:D)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66">
+      <c r="H66" s="242" t="inlineStr">
+        <is>
+          <t>⑥ TOCOL / TOROW ｜ データの縦横を変換</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="H67" s="241" t="inlineStr">
+        <is>
+          <t>TOCOL＝横→縦、TOROW＝縦→横。貼り付け方向を直したい時に。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="H68" s="248" t="inlineStr">
+        <is>
+          <t>横入力→</t>
+        </is>
+      </c>
+      <c r="I68" s="249" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="J68" s="249" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="K68" s="249" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="L68" s="249" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="M68" s="249" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="H69" s="241" t="inlineStr">
+        <is>
+          <t>↓ TOCOL で縦1列に</t>
+        </is>
+      </c>
+      <c r="J69" s="241" t="inlineStr">
+        <is>
+          <t>→ TOROW で C8:C10 を横1行に</t>
+        </is>
       </c>
     </row>
     <row r="70">
-      <c r="B70" s="199" t="inlineStr">
-        <is>
-          <t>⑤ FILTER + SORTBY ｜ ヘッダー行を除いて抽出→売上の降順</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="198" t="inlineStr">
-        <is>
-          <t>参照をB8(見出しの下)から始めるとヘッダーは自然に除外。空白行はFILTERで除外し、SORTBYで売上降順。</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="204">
-        <f>SORTBY(FILTER(B8:E16,C8:C16&lt;&gt;""),FILTER(E8:E16,C8:C16&lt;&gt;""),-1)</f>
-        <v/>
+      <c r="H70" s="247">
+        <f t="array" ref="H70:H74">_xlfn.TOCOL(I68:M68)</f>
+        <v/>
+      </c>
+      <c r="J70" s="247">
+        <f t="array" ref="J70:L70">_xlfn.TOROW(D8:D10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80">
+      <c r="H80" s="242" t="inlineStr">
+        <is>
+          <t>⑦ TOCOL + TEXTSPLIT ｜ カンマ区切り文字列を縦1列に</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="H81" s="241" t="inlineStr">
+        <is>
+          <t>web/PDFの表を貼れない時、カンマ区切りテキストを縦のリストに展開できる。</t>
+        </is>
       </c>
     </row>
     <row r="82">
-      <c r="B82" s="199" t="inlineStr">
-        <is>
-          <t>⑥ TOCOL / TOROW ｜ データの縦横を変換</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="B83" s="198" t="inlineStr">
-        <is>
-          <t>TOCOL＝横→縦、TOROW＝縦→横。貼り付け方向を直したい時に。</t>
-        </is>
-      </c>
-    </row>
+      <c r="H82" s="248" t="inlineStr">
+        <is>
+          <t>入力→</t>
+        </is>
+      </c>
+      <c r="I82" s="250" t="inlineStr">
+        <is>
+          <t>りんご,みかん,ぶどう,いちご,かき</t>
+        </is>
+      </c>
+    </row>
+    <row r="83"/>
     <row r="84">
-      <c r="B84" s="205" t="inlineStr">
-        <is>
-          <t>横入力→</t>
-        </is>
-      </c>
-      <c r="C84" s="206" t="inlineStr">
-        <is>
-          <t>月</t>
-        </is>
-      </c>
-      <c r="D84" s="206" t="inlineStr">
-        <is>
-          <t>火</t>
-        </is>
-      </c>
-      <c r="E84" s="206" t="inlineStr">
-        <is>
-          <t>水</t>
-        </is>
-      </c>
-      <c r="F84" s="206" t="inlineStr">
-        <is>
-          <t>木</t>
-        </is>
-      </c>
-      <c r="G84" s="206" t="inlineStr">
-        <is>
-          <t>金</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="B85" s="198" t="inlineStr">
-        <is>
-          <t>↓ TOCOL で縦1列に</t>
-        </is>
-      </c>
-      <c r="D85" s="198" t="inlineStr">
-        <is>
-          <t>→ TOROW で C8:C10 を横1行に</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="B86" s="204">
-        <f>TOCOL(C84:G84)</f>
-        <v/>
-      </c>
-      <c r="D86" s="204">
-        <f>TOROW(C8:C10)</f>
-        <v/>
+      <c r="H84" s="247">
+        <f t="array" ref="H84:H88">_xlfn.TOCOL(_xlfn.TEXTSPLIT(I82,","))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94">
+      <c r="H94" s="242" t="inlineStr">
+        <is>
+          <t>⑧ SEQUENCE + ROWS ｜ データ件数ぶんの連番を自動生成</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="H95" s="241" t="inlineStr">
+        <is>
+          <t>ROWS で件数を数え、その数だけ連番を作る。行が増減しても自動追従。</t>
+        </is>
       </c>
     </row>
     <row r="96">
-      <c r="B96" s="199" t="inlineStr">
-        <is>
-          <t>⑦ TOCOL + TEXTSPLIT ｜ カンマ区切り文字列を縦1列に</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="B97" s="198" t="inlineStr">
-        <is>
-          <t>web/PDFの表を貼れない時、カンマ区切りテキストを縦のリストに展開できる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="B98" s="205" t="inlineStr">
-        <is>
-          <t>入力→</t>
-        </is>
-      </c>
-      <c r="C98" s="207" t="inlineStr">
-        <is>
-          <t>りんご,みかん,ぶどう,いちご,かき</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="B100" s="204">
-        <f>TOCOL(TEXTSPLIT(C98,","))</f>
-        <v/>
-      </c>
+      <c r="H96" s="247">
+        <f t="array" ref="H96:H100">_xlfn.SEQUENCE(ROWS(_xlfn.ANCHORARRAY(H44)))</f>
+        <v/>
+      </c>
+      <c r="I96" s="247">
+        <f t="array" ref="I96:I100">_xlfn.ANCHORARRAY(H44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102">
+      <c r="H102" s="199" t="inlineStr">
+        <is>
+          <t>⑨ EOMONTH + SEQUENCE ｜ 5年分の“月初(X月1日)”を横にスピル</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="H103" s="198" t="inlineStr">
+        <is>
+          <t>SEQUENCE(1,60,0) で 0〜59 か月を作り、EOMONTH(基準,n)+1 で各月の1日に。基準日を変えると全体が動く。</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="H104" s="253" t="inlineStr">
+        <is>
+          <t>基準日→</t>
+        </is>
+      </c>
+      <c r="I104" s="254" t="n">
+        <v>46037</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="H105" s="255">
+        <f>EOMONTH(I104,_xlfn.SEQUENCE(1,60,0))+1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="H106" s="198" t="inlineStr">
+        <is>
+          <t>↑ H105から右へ60列（5年＝60か月）ぶんの月初がスピルします。</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="H107" s="242" t="inlineStr">
+        <is>
+          <t>▼ 問題（黄色セルに自分で数式を入れてみよう。解答は右のI列）</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="H108" s="251" t="inlineStr">
+        <is>
+          <t>問題</t>
+        </is>
+      </c>
+      <c r="I108" s="209" t="n"/>
+      <c r="J108" s="209" t="n"/>
+      <c r="K108" s="209" t="n"/>
+      <c r="L108" s="210" t="n"/>
+      <c r="M108" s="252" t="inlineStr">
+        <is>
+          <t>解答欄</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="H109" s="245" t="inlineStr">
+        <is>
+          <t>Q1  C列から空白を除いた重複なしリストを作る</t>
+        </is>
+      </c>
+      <c r="I109" s="209" t="n"/>
+      <c r="J109" s="209" t="n"/>
+      <c r="K109" s="209" t="n"/>
+      <c r="L109" s="210" t="n"/>
+      <c r="M109" s="250" t="n"/>
     </row>
     <row r="110">
-      <c r="B110" s="199" t="inlineStr">
-        <is>
-          <t>⑧ SEQUENCE + ROWS ｜ データ件数ぶんの連番を自動生成</t>
-        </is>
-      </c>
+      <c r="H110" s="245" t="inlineStr">
+        <is>
+          <t>Q2  Q1に加えて『合計』も除外し、実データのみのリストにする</t>
+        </is>
+      </c>
+      <c r="I110" s="209" t="n"/>
+      <c r="J110" s="209" t="n"/>
+      <c r="K110" s="209" t="n"/>
+      <c r="L110" s="210" t="n"/>
+      <c r="M110" s="250" t="n"/>
     </row>
     <row r="111">
-      <c r="B111" s="198" t="inlineStr">
-        <is>
-          <t>ROWS で件数を数え、その数だけ連番を作る。行が増減しても自動追従。</t>
-        </is>
-      </c>
+      <c r="H111" s="245" t="inlineStr">
+        <is>
+          <t>Q3  空白でない行だけを抽出し、売上の降順に並べ替える（ヘッダー除く）</t>
+        </is>
+      </c>
+      <c r="I111" s="209" t="n"/>
+      <c r="J111" s="209" t="n"/>
+      <c r="K111" s="209" t="n"/>
+      <c r="L111" s="210" t="n"/>
+      <c r="M111" s="250" t="n"/>
     </row>
     <row r="112">
-      <c r="B112" s="198" t="inlineStr">
-        <is>
-          <t>元データ10行ぶんの連番</t>
-        </is>
-      </c>
-      <c r="D112" s="198" t="inlineStr">
-        <is>
-          <t>②の実データ件数ぶんの連番</t>
-        </is>
-      </c>
+      <c r="H112" s="245" t="inlineStr">
+        <is>
+          <t>Q4  文字列『東京,大阪,名古屋』を縦1列に展開する</t>
+        </is>
+      </c>
+      <c r="I112" s="209" t="n"/>
+      <c r="J112" s="209" t="n"/>
+      <c r="K112" s="209" t="n"/>
+      <c r="L112" s="210" t="n"/>
+      <c r="M112" s="250" t="n"/>
     </row>
     <row r="113">
-      <c r="B113" s="204">
-        <f>SEQUENCE(ROWS(C8:C17))</f>
-        <v/>
-      </c>
-      <c r="D113" s="204">
-        <f>SEQUENCE(ROWS(UNIQUE(TOCOL(FILTER(C8:C17,C8:C17&lt;&gt;"合計"),1))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="124">
-      <c r="B124" s="199" t="inlineStr">
-        <is>
-          <t>▼ 問題（黄色セルに自分で数式を入れてみよう。解答は右のI列）</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="B125" s="208" t="inlineStr">
-        <is>
-          <t>問題</t>
-        </is>
-      </c>
-      <c r="C125" s="209" t="n"/>
-      <c r="D125" s="209" t="n"/>
-      <c r="E125" s="209" t="n"/>
-      <c r="F125" s="210" t="n"/>
-      <c r="G125" s="211" t="inlineStr">
-        <is>
-          <t>解答欄</t>
-        </is>
-      </c>
-      <c r="I125" s="208" t="inlineStr">
-        <is>
-          <t>解答例</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="B126" s="202" t="inlineStr">
-        <is>
-          <t>Q1  C列から空白を除いた重複なしリストを作る</t>
-        </is>
-      </c>
-      <c r="C126" s="209" t="n"/>
-      <c r="D126" s="209" t="n"/>
-      <c r="E126" s="209" t="n"/>
-      <c r="F126" s="210" t="n"/>
-      <c r="G126" s="207" t="n"/>
-      <c r="I126" s="202" t="inlineStr">
-        <is>
-          <t>=UNIQUE(TOCOL(C8:C17,1))</t>
-        </is>
-      </c>
-      <c r="J126" s="209" t="n"/>
-      <c r="K126" s="210" t="n"/>
-    </row>
-    <row r="127">
-      <c r="B127" s="202" t="inlineStr">
-        <is>
-          <t>Q2  Q1に加えて『合計』も除外し、実データのみのリストにする</t>
-        </is>
-      </c>
-      <c r="C127" s="209" t="n"/>
-      <c r="D127" s="209" t="n"/>
-      <c r="E127" s="209" t="n"/>
-      <c r="F127" s="210" t="n"/>
-      <c r="G127" s="207" t="n"/>
-      <c r="I127" s="202" t="inlineStr">
-        <is>
-          <t>=UNIQUE(TOCOL(FILTER(C8:C17,C8:C17&lt;&gt;"合計"),1))</t>
-        </is>
-      </c>
-      <c r="J127" s="209" t="n"/>
-      <c r="K127" s="210" t="n"/>
-    </row>
-    <row r="128">
-      <c r="B128" s="202" t="inlineStr">
-        <is>
-          <t>Q3  空白でない行だけを抽出し、売上の降順に並べ替える（ヘッダー除く）</t>
-        </is>
-      </c>
-      <c r="C128" s="209" t="n"/>
-      <c r="D128" s="209" t="n"/>
-      <c r="E128" s="209" t="n"/>
-      <c r="F128" s="210" t="n"/>
-      <c r="G128" s="207" t="n"/>
-      <c r="I128" s="202" t="inlineStr">
-        <is>
-          <t>=SORTBY(FILTER(B8:E16,C8:C16&lt;&gt;""),FILTER(E8:E16,C8:C16&lt;&gt;""),-1)</t>
-        </is>
-      </c>
-      <c r="J128" s="209" t="n"/>
-      <c r="K128" s="210" t="n"/>
-    </row>
-    <row r="129">
-      <c r="B129" s="202" t="inlineStr">
-        <is>
-          <t>Q4  文字列『東京,大阪,名古屋』を縦1列に展開する</t>
-        </is>
-      </c>
-      <c r="C129" s="209" t="n"/>
-      <c r="D129" s="209" t="n"/>
-      <c r="E129" s="209" t="n"/>
-      <c r="F129" s="210" t="n"/>
-      <c r="G129" s="207" t="n"/>
-      <c r="I129" s="202" t="inlineStr">
-        <is>
-          <t>=TOCOL(TEXTSPLIT("東京,大阪,名古屋",","))</t>
-        </is>
-      </c>
-      <c r="J129" s="209" t="n"/>
-      <c r="K129" s="210" t="n"/>
-    </row>
-    <row r="130">
-      <c r="B130" s="202" t="inlineStr">
+      <c r="H113" s="245" t="inlineStr">
         <is>
           <t>Q5  元データの件数ぶん（10行）の連番を作る</t>
         </is>
       </c>
-      <c r="C130" s="209" t="n"/>
-      <c r="D130" s="209" t="n"/>
-      <c r="E130" s="209" t="n"/>
-      <c r="F130" s="210" t="n"/>
-      <c r="G130" s="207" t="n"/>
-      <c r="I130" s="202" t="inlineStr">
-        <is>
-          <t>=SEQUENCE(ROWS(C8:C17))</t>
-        </is>
-      </c>
-      <c r="J130" s="209" t="n"/>
-      <c r="K130" s="210" t="n"/>
+      <c r="I113" s="209" t="n"/>
+      <c r="J113" s="209" t="n"/>
+      <c r="K113" s="209" t="n"/>
+      <c r="L113" s="210" t="n"/>
+      <c r="M113" s="250" t="n"/>
+    </row>
+    <row r="114">
+      <c r="H114" s="256" t="inlineStr">
+        <is>
+          <t>Q6  基準日セルから5年分（60か月）の月初（1日）を横1行にスピルする</t>
+        </is>
+      </c>
+      <c r="I114" s="209" t="n"/>
+      <c r="J114" s="209" t="n"/>
+      <c r="K114" s="209" t="n"/>
+      <c r="L114" s="210" t="n"/>
+      <c r="M114" s="257" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="B126:F126"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B125:F125"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B46:F46"/>
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="I127:K127"/>
-    <mergeCell ref="I130:K130"/>
-    <mergeCell ref="B96:F96"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B70:F70"/>
-    <mergeCell ref="B130:F130"/>
-    <mergeCell ref="B82:F82"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="I128:K128"/>
-    <mergeCell ref="B128:F128"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="I126:K126"/>
-    <mergeCell ref="B110:F110"/>
-    <mergeCell ref="I129:K129"/>
+  <mergeCells count="18">
+    <mergeCell ref="H108:L108"/>
+    <mergeCell ref="H30:L30"/>
+    <mergeCell ref="H114:L114"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="H109:L109"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="H42:L42"/>
+    <mergeCell ref="H54:L54"/>
+    <mergeCell ref="H112:L112"/>
+    <mergeCell ref="H18:L18"/>
+    <mergeCell ref="H66:L66"/>
+    <mergeCell ref="H94:L94"/>
+    <mergeCell ref="H102:L102"/>
+    <mergeCell ref="H80:L80"/>
+    <mergeCell ref="H110:L110"/>
+    <mergeCell ref="H113:L113"/>
+    <mergeCell ref="H107:L107"/>
+    <mergeCell ref="H111:L111"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6935,7 +7066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="B2:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
     <col width="2.36328125" customWidth="1" min="1" max="3"/>
@@ -6944,7 +7075,6 @@
     <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="19.5" customHeight="1">
       <c r="B2" s="64" t="inlineStr">
         <is>
@@ -7164,7 +7294,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="B2:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
     <col width="2.36328125" customWidth="1" min="1" max="3"/>
@@ -7173,7 +7303,6 @@
     <col width="34" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="19.5" customHeight="1">
       <c r="B2" s="64" t="inlineStr">
         <is>

--- a/files/excel-mastery-full.xlsx
+++ b/files/excel-mastery-full.xlsx
@@ -6024,11 +6024,11 @@
         <v>160000</v>
       </c>
       <c r="H8" s="247">
-        <f t="array" ref="H8:H14">_xlfn.UNIQUE(D:D)</f>
+        <f>_xlfn.UNIQUE(D:D)</f>
         <v/>
       </c>
       <c r="J8" s="247">
-        <f t="array" ref="J8:J13">_xlfn.UNIQUE(_xlfn.TOCOL(D:D,1))</f>
+        <f>_xlfn.UNIQUE(_xlfn.TOCOL(D:D,1))</f>
         <v/>
       </c>
     </row>
@@ -6245,7 +6245,7 @@
     </row>
     <row r="20">
       <c r="H20" s="247">
-        <f t="array" ref="H20:H24">_xlfn.UNIQUE(_xlfn.TOCOL(_xlfn._xlws.FILTER(D:D,D:D&lt;&gt;"予約経路"),1))</f>
+        <f>_xlfn.UNIQUE(_xlfn.TOCOL(_xlfn._xlws.FILTER(D:D,D:D&lt;&gt;"予約経路"),1))</f>
         <v/>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
     </row>
     <row r="32">
       <c r="H32" s="247">
-        <f t="array" ref="H32:H36">_xlfn.UNIQUE(_xlfn.TOCOL(_xlfn.DROP(D:D,7),1))</f>
+        <f>_xlfn.UNIQUE(_xlfn.TOCOL(_xlfn.DROP(D:D,7),1))</f>
         <v/>
       </c>
     </row>
@@ -6303,7 +6303,7 @@
     </row>
     <row r="44">
       <c r="H44" s="247">
-        <f t="array" ref="H44:H48">_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn.TOCOL(_xlfn.DROP(D:D,7),1)),1,-1)</f>
+        <f>_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn.TOCOL(_xlfn.DROP(D:D,7),1)),1,-1)</f>
         <v/>
       </c>
     </row>
@@ -6332,15 +6332,11 @@
     </row>
     <row r="56">
       <c r="H56" s="247">
-        <f t="array" ref="H56:H60">_xlfn.SORTBY(
-                _xlfn.UNIQUE(_xlfn.TOCOL(_xlfn.DROP(C:C,7),1)),
-                _xlfn.UNIQUE(_xlfn.TOCOL(_xlfn.DROP(C:C,7),1)),
-                1
-               )</f>
+        <f>_xlfn.SORTBY(_xlfn.UNIQUE(_xlfn.TOCOL(_xlfn.DROP(C:C,7),1)),_xlfn.UNIQUE(_xlfn.TOCOL(_xlfn.DROP(C:C,7),1)),1)</f>
         <v/>
       </c>
       <c r="I56" s="247">
-        <f t="array" ref="I56:I60">_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(H56),C:C,D:D)</f>
+        <f>_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(H56),C:C,D:D)</f>
         <v/>
       </c>
     </row>
@@ -6413,11 +6409,11 @@
     </row>
     <row r="70">
       <c r="H70" s="247">
-        <f t="array" ref="H70:H74">_xlfn.TOCOL(I68:M68)</f>
+        <f>_xlfn.TOCOL(I68:M68)</f>
         <v/>
       </c>
       <c r="J70" s="247">
-        <f t="array" ref="J70:L70">_xlfn.TOROW(D8:D10)</f>
+        <f>_xlfn.TOROW(D8:D10)</f>
         <v/>
       </c>
     </row>
@@ -6459,7 +6455,7 @@
     <row r="83"/>
     <row r="84">
       <c r="H84" s="247">
-        <f t="array" ref="H84:H88">_xlfn.TOCOL(_xlfn.TEXTSPLIT(I82,","))</f>
+        <f>_xlfn.TOCOL(_xlfn.TEXTSPLIT(I82,","))</f>
         <v/>
       </c>
     </row>
@@ -6488,11 +6484,11 @@
     </row>
     <row r="96">
       <c r="H96" s="247">
-        <f t="array" ref="H96:H100">_xlfn.SEQUENCE(ROWS(_xlfn.ANCHORARRAY(H44)))</f>
+        <f>_xlfn.SEQUENCE(ROWS(_xlfn.ANCHORARRAY(H44)))</f>
         <v/>
       </c>
       <c r="I96" s="247">
-        <f t="array" ref="I96:I100">_xlfn.ANCHORARRAY(H44)</f>
+        <f>_xlfn.ANCHORARRAY(H44)</f>
         <v/>
       </c>
     </row>

--- a/files/excel-mastery-full.xlsx
+++ b/files/excel-mastery-full.xlsx
@@ -43,7 +43,7 @@
     <numFmt numFmtId="170" formatCode="0.000"/>
     <numFmt numFmtId="171" formatCode="yyyy/m/d"/>
   </numFmts>
-  <fonts count="41">
+  <fonts count="42">
     <font>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
@@ -326,8 +326,13 @@
     <font>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFC00000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -380,6 +385,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF6D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -733,7 +743,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="258">
+  <cellXfs count="259">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -1450,6 +1460,9 @@
     <xf numFmtId="171" fontId="40" fillId="9" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="10" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -5948,7 +5961,13 @@
       </c>
       <c r="C3" s="241" t="n"/>
     </row>
-    <row r="4"/>
+    <row r="4" ht="20" customHeight="1">
+      <c r="B4" s="258" t="inlineStr">
+        <is>
+          <t>⚠ 開いたとき数式の先頭に「@」が付く場合があります（例：=@UNIQUE(…)）。その時は数式バーで式の中の「@」をすべて削除し、Enter で確定し直すと正しくスピルします。</t>
+        </is>
+      </c>
+    </row>
     <row r="5"/>
     <row r="6">
       <c r="B6" s="242" t="inlineStr">
@@ -6630,25 +6649,26 @@
       <c r="M114" s="257" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="H108:L108"/>
+  <mergeCells count="19">
     <mergeCell ref="H30:L30"/>
-    <mergeCell ref="H114:L114"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="H109:L109"/>
-    <mergeCell ref="H6:L6"/>
-    <mergeCell ref="H42:L42"/>
     <mergeCell ref="H54:L54"/>
     <mergeCell ref="H112:L112"/>
+    <mergeCell ref="H102:L102"/>
+    <mergeCell ref="H113:L113"/>
+    <mergeCell ref="H114:L114"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="H94:L94"/>
+    <mergeCell ref="H110:L110"/>
+    <mergeCell ref="H108:L108"/>
+    <mergeCell ref="H109:L109"/>
+    <mergeCell ref="H66:L66"/>
+    <mergeCell ref="H80:L80"/>
+    <mergeCell ref="B4:M4"/>
+    <mergeCell ref="H111:L111"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="H42:L42"/>
     <mergeCell ref="H18:L18"/>
-    <mergeCell ref="H66:L66"/>
-    <mergeCell ref="H94:L94"/>
-    <mergeCell ref="H102:L102"/>
-    <mergeCell ref="H80:L80"/>
-    <mergeCell ref="H110:L110"/>
-    <mergeCell ref="H113:L113"/>
     <mergeCell ref="H107:L107"/>
-    <mergeCell ref="H111:L111"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
